--- a/CP_SAT_排产结果.xlsx
+++ b/CP_SAT_排产结果.xlsx
@@ -11,7 +11,7 @@
     <sheet name="5月排产图" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'表1_订单视图'!$A$2:$Z$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'表1_订单视图'!$A$2:$Z$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'5月排产图'!$A$2:$AF$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -43,7 +43,7 @@
       <color rgb="00000000"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -85,6 +85,16 @@
         <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0E0E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -118,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -154,10 +164,10 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -172,19 +182,34 @@
     <xf numFmtId="3" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -555,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -757,25 +782,25 @@
         </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>6210000</v>
+        <v>12420000</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>6210000</v>
+        <v>12420000</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>8</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>3.375</v>
+        <v>6.75</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>338</v>
+        <v>675</v>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
@@ -789,40 +814,40 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="R3" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>6210000</v>
+        <v>12420000</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>8073000</v>
+        <v>12880000</v>
       </c>
       <c r="V3" s="4" t="inlineStr"/>
       <c r="W3" s="4" t="n">
-        <v>1863000</v>
+        <v>460000</v>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Y3" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z3" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -857,25 +882,25 @@
         </is>
       </c>
       <c r="G4" s="4" t="n">
-        <v>6210000</v>
+        <v>16560000</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>6210000</v>
+        <v>16560000</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>3.375</v>
+        <v>6</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>338</v>
+        <v>600</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -884,7 +909,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -894,24 +919,24 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="R4" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="T4" s="4" t="n">
-        <v>6210000</v>
+        <v>16560000</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>6738492</v>
+        <v>17480000</v>
       </c>
       <c r="V4" s="4" t="inlineStr"/>
       <c r="W4" s="4" t="n">
-        <v>528492</v>
+        <v>920000</v>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
@@ -957,19 +982,19 @@
         </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>4140000</v>
+        <v>24840000</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>4140000</v>
+        <v>24840000</v>
       </c>
       <c r="J5" s="4" t="n">
+        <v>108</v>
+      </c>
+      <c r="K5" s="4" t="n">
         <v>18</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="L5" s="5" t="n">
         <v>6</v>
@@ -979,39 +1004,39 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="R5" s="4" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>4140000</v>
+        <v>24840000</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>4480574</v>
+        <v>25039599</v>
       </c>
       <c r="V5" s="4" t="inlineStr"/>
       <c r="W5" s="4" t="n">
-        <v>340574</v>
+        <v>199599</v>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
@@ -1057,61 +1082,61 @@
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>4140000</v>
+        <v>13800000</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4140000</v>
+        <v>13800000</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>6</v>
+        <v>4.6154</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>600</v>
+        <v>462</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="R6" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>4140000</v>
+        <v>13800000</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>4347000</v>
+        <v>13801563</v>
       </c>
       <c r="V6" s="4" t="inlineStr"/>
       <c r="W6" s="4" t="n">
-        <v>207000</v>
+        <v>1563</v>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
@@ -1157,61 +1182,61 @@
         </is>
       </c>
       <c r="G7" s="4" t="n">
-        <v>4140000</v>
+        <v>9660000</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4140000</v>
+        <v>9660000</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>225</v>
+        <v>350</v>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="R7" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>4140000</v>
+        <v>9660000</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>4649410</v>
+        <v>9660000</v>
       </c>
       <c r="V7" s="4" t="inlineStr"/>
       <c r="W7" s="4" t="n">
-        <v>509410</v>
+        <v>0</v>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
@@ -1225,8 +1250,208 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>原订单</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>8280000</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>8280000</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>3.2727</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>328</v>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>8280000</v>
+      </c>
+      <c r="U8" s="4" t="n">
+        <v>8280000</v>
+      </c>
+      <c r="V8" s="4" t="inlineStr"/>
+      <c r="W8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>原订单</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>11040000</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>11040000</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>600</v>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="R9" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S9" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>11040000</v>
+      </c>
+      <c r="U9" s="4" t="n">
+        <v>11040000</v>
+      </c>
+      <c r="V9" s="4" t="inlineStr"/>
+      <c r="W9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Y9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:Z7"/>
+  <autoFilter ref="A2:Z9"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Z1"/>
   </mergeCells>
@@ -1240,7 +1465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF75"/>
+  <dimension ref="A1:AF96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1454,71 +1679,139 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J3" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K3" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>停电检修</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="N3" s="9" t="inlineStr">
         <is>
           <t>停电检修</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K3" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr"/>
-      <c r="V3" s="3" t="inlineStr"/>
-      <c r="W3" s="3" t="inlineStr"/>
-      <c r="X3" s="3" t="inlineStr"/>
-      <c r="Y3" s="3" t="inlineStr"/>
-      <c r="Z3" s="3" t="inlineStr"/>
-      <c r="AA3" s="3" t="inlineStr"/>
-      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="O3" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P3" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q3" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R3" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S3" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W3" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X3" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y3" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="Z3" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="AA3" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="AB3" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
       <c r="AC3" s="3" t="inlineStr"/>
       <c r="AD3" s="3" t="inlineStr"/>
       <c r="AE3" s="3" t="inlineStr"/>
@@ -1532,71 +1825,139 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M4" s="9" t="inlineStr">
         <is>
           <t>停电检修</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="N4" s="9" t="inlineStr">
         <is>
           <t>停电检修</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K4" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr"/>
-      <c r="N4" s="3" t="inlineStr"/>
-      <c r="O4" s="3" t="inlineStr"/>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="inlineStr"/>
-      <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="3" t="inlineStr"/>
-      <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="3" t="inlineStr"/>
-      <c r="W4" s="3" t="inlineStr"/>
-      <c r="X4" s="3" t="inlineStr"/>
-      <c r="Y4" s="3" t="inlineStr"/>
-      <c r="Z4" s="3" t="inlineStr"/>
-      <c r="AA4" s="3" t="inlineStr"/>
-      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="O4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y4" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="Z4" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="AA4" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="AB4" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
       <c r="AC4" s="3" t="inlineStr"/>
       <c r="AD4" s="3" t="inlineStr"/>
       <c r="AE4" s="3" t="inlineStr"/>
@@ -1610,71 +1971,139 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M5" s="9" t="inlineStr">
         <is>
           <t>停电检修</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="N5" s="9" t="inlineStr">
         <is>
           <t>停电检修</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="3" t="inlineStr"/>
-      <c r="V5" s="3" t="inlineStr"/>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="inlineStr"/>
-      <c r="Y5" s="3" t="inlineStr"/>
-      <c r="Z5" s="3" t="inlineStr"/>
-      <c r="AA5" s="3" t="inlineStr"/>
-      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P5" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q5" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R5" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S5" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W5" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X5" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y5" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="Z5" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="AA5" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="AB5" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
       <c r="AC5" s="3" t="inlineStr"/>
       <c r="AD5" s="3" t="inlineStr"/>
       <c r="AE5" s="3" t="inlineStr"/>
@@ -1688,71 +2117,139 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M6" s="9" t="inlineStr">
         <is>
           <t>停电检修</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="N6" s="9" t="inlineStr">
         <is>
           <t>停电检修</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr"/>
-      <c r="N6" s="3" t="inlineStr"/>
-      <c r="O6" s="3" t="inlineStr"/>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr"/>
-      <c r="U6" s="3" t="inlineStr"/>
-      <c r="V6" s="3" t="inlineStr"/>
-      <c r="W6" s="3" t="inlineStr"/>
-      <c r="X6" s="3" t="inlineStr"/>
-      <c r="Y6" s="3" t="inlineStr"/>
-      <c r="Z6" s="3" t="inlineStr"/>
-      <c r="AA6" s="3" t="inlineStr"/>
-      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="O6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y6" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="Z6" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="AA6" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="AB6" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
       <c r="AC6" s="3" t="inlineStr"/>
       <c r="AD6" s="3" t="inlineStr"/>
       <c r="AE6" s="3" t="inlineStr"/>
@@ -1766,71 +2263,139 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M7" s="9" t="inlineStr">
         <is>
           <t>停电检修</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="N7" s="9" t="inlineStr">
         <is>
           <t>停电检修</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J7" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K7" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr"/>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr"/>
-      <c r="U7" s="3" t="inlineStr"/>
-      <c r="V7" s="3" t="inlineStr"/>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="3" t="inlineStr"/>
-      <c r="Y7" s="3" t="inlineStr"/>
-      <c r="Z7" s="3" t="inlineStr"/>
-      <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="O7" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P7" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R7" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S7" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W7" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X7" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y7" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="Z7" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="AA7" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="AB7" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
       <c r="AC7" s="3" t="inlineStr"/>
       <c r="AD7" s="3" t="inlineStr"/>
       <c r="AE7" s="3" t="inlineStr"/>
@@ -1844,71 +2409,139 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
         <is>
           <t>停电检修</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="N8" s="9" t="inlineStr">
         <is>
           <t>停电检修</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K8" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr"/>
-      <c r="N8" s="3" t="inlineStr"/>
-      <c r="O8" s="3" t="inlineStr"/>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr"/>
-      <c r="U8" s="3" t="inlineStr"/>
-      <c r="V8" s="3" t="inlineStr"/>
-      <c r="W8" s="3" t="inlineStr"/>
-      <c r="X8" s="3" t="inlineStr"/>
-      <c r="Y8" s="3" t="inlineStr"/>
-      <c r="Z8" s="3" t="inlineStr"/>
-      <c r="AA8" s="3" t="inlineStr"/>
-      <c r="AB8" s="3" t="inlineStr"/>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y8" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="Z8" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="AA8" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="AB8" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
       <c r="AC8" s="3" t="inlineStr"/>
       <c r="AD8" s="3" t="inlineStr"/>
       <c r="AE8" s="3" t="inlineStr"/>
@@ -1920,73 +2553,141 @@
           <t>Line 7</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>停电检修</t>
+        </is>
+      </c>
+      <c r="N9" s="9" t="inlineStr">
+        <is>
+          <t>停电检修</t>
+        </is>
+      </c>
+      <c r="O9" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P9" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q9" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R9" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S9" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T9" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="U9" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="V9" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>停电检修</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>停电检修</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="X9" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K9" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr"/>
-      <c r="N9" s="3" t="inlineStr"/>
-      <c r="O9" s="3" t="inlineStr"/>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr"/>
-      <c r="T9" s="3" t="inlineStr"/>
-      <c r="U9" s="3" t="inlineStr"/>
-      <c r="V9" s="3" t="inlineStr"/>
-      <c r="W9" s="3" t="inlineStr"/>
-      <c r="X9" s="3" t="inlineStr"/>
-      <c r="Y9" s="3" t="inlineStr"/>
-      <c r="Z9" s="3" t="inlineStr"/>
-      <c r="AA9" s="3" t="inlineStr"/>
-      <c r="AB9" s="3" t="inlineStr"/>
+      <c r="Y9" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="Z9" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="AA9" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="AB9" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
       <c r="AC9" s="3" t="inlineStr"/>
       <c r="AD9" s="3" t="inlineStr"/>
       <c r="AE9" s="3" t="inlineStr"/>
@@ -1998,73 +2699,141 @@
           <t>Line 8</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M10" s="9" t="inlineStr">
+        <is>
+          <t>停电检修</t>
+        </is>
+      </c>
+      <c r="N10" s="9" t="inlineStr">
+        <is>
+          <t>停电检修</t>
+        </is>
+      </c>
+      <c r="O10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q10" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="R10" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="S10" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>停电检修</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>停电检修</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="T10" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="U10" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="V10" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="J10" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K10" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr"/>
-      <c r="N10" s="3" t="inlineStr"/>
-      <c r="O10" s="3" t="inlineStr"/>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr"/>
-      <c r="U10" s="3" t="inlineStr"/>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" s="3" t="inlineStr"/>
-      <c r="X10" s="3" t="inlineStr"/>
-      <c r="Y10" s="3" t="inlineStr"/>
-      <c r="Z10" s="3" t="inlineStr"/>
-      <c r="AA10" s="3" t="inlineStr"/>
-      <c r="AB10" s="3" t="inlineStr"/>
+      <c r="W10" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="X10" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Y10" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="Z10" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="AA10" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="AB10" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
       <c r="AC10" s="3" t="inlineStr"/>
       <c r="AD10" s="3" t="inlineStr"/>
       <c r="AE10" s="3" t="inlineStr"/>
@@ -2076,73 +2845,141 @@
           <t>Line 9</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M11" s="9" t="inlineStr">
+        <is>
+          <t>停电检修</t>
+        </is>
+      </c>
+      <c r="N11" s="9" t="inlineStr">
+        <is>
+          <t>停电检修</t>
+        </is>
+      </c>
+      <c r="O11" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="P11" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="Q11" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>停电检修</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>停电检修</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="R11" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="S11" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="T11" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="J11" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K11" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr"/>
-      <c r="N11" s="3" t="inlineStr"/>
-      <c r="O11" s="3" t="inlineStr"/>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr"/>
-      <c r="U11" s="3" t="inlineStr"/>
-      <c r="V11" s="3" t="inlineStr"/>
-      <c r="W11" s="3" t="inlineStr"/>
-      <c r="X11" s="3" t="inlineStr"/>
-      <c r="Y11" s="3" t="inlineStr"/>
-      <c r="Z11" s="3" t="inlineStr"/>
-      <c r="AA11" s="3" t="inlineStr"/>
-      <c r="AB11" s="3" t="inlineStr"/>
+      <c r="U11" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="V11" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="W11" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="X11" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Y11" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="Z11" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="AA11" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="AB11" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
       <c r="AC11" s="3" t="inlineStr"/>
       <c r="AD11" s="3" t="inlineStr"/>
       <c r="AE11" s="3" t="inlineStr"/>
@@ -2154,73 +2991,141 @@
           <t>Line 10</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M12" s="9" t="inlineStr">
+        <is>
+          <t>停电检修</t>
+        </is>
+      </c>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
+          <t>停电检修</t>
+        </is>
+      </c>
+      <c r="O12" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="P12" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="Q12" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>停电检修</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>停电检修</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="J12" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K12" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr"/>
-      <c r="N12" s="3" t="inlineStr"/>
-      <c r="O12" s="3" t="inlineStr"/>
-      <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr"/>
-      <c r="S12" s="3" t="inlineStr"/>
-      <c r="T12" s="3" t="inlineStr"/>
-      <c r="U12" s="3" t="inlineStr"/>
-      <c r="V12" s="3" t="inlineStr"/>
-      <c r="W12" s="3" t="inlineStr"/>
-      <c r="X12" s="3" t="inlineStr"/>
-      <c r="Y12" s="3" t="inlineStr"/>
-      <c r="Z12" s="3" t="inlineStr"/>
-      <c r="AA12" s="3" t="inlineStr"/>
-      <c r="AB12" s="3" t="inlineStr"/>
+      <c r="R12" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="S12" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="T12" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="U12" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="V12" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="W12" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="X12" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Y12" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="Z12" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="AA12" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="AB12" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
       <c r="AC12" s="3" t="inlineStr"/>
       <c r="AD12" s="3" t="inlineStr"/>
       <c r="AE12" s="3" t="inlineStr"/>
@@ -2232,73 +3137,141 @@
           <t>Line 11</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M13" s="9" t="inlineStr">
+        <is>
+          <t>停电检修</t>
+        </is>
+      </c>
+      <c r="N13" s="9" t="inlineStr">
+        <is>
+          <t>停电检修</t>
+        </is>
+      </c>
+      <c r="O13" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="P13" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="Q13" s="11" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>停电检修</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>停电检修</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H13" s="11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I13" s="11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="J13" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K13" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr"/>
-      <c r="M13" s="3" t="inlineStr"/>
-      <c r="N13" s="3" t="inlineStr"/>
-      <c r="O13" s="3" t="inlineStr"/>
-      <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="3" t="inlineStr"/>
-      <c r="R13" s="3" t="inlineStr"/>
-      <c r="S13" s="3" t="inlineStr"/>
-      <c r="T13" s="3" t="inlineStr"/>
-      <c r="U13" s="3" t="inlineStr"/>
-      <c r="V13" s="3" t="inlineStr"/>
-      <c r="W13" s="3" t="inlineStr"/>
-      <c r="X13" s="3" t="inlineStr"/>
-      <c r="Y13" s="3" t="inlineStr"/>
-      <c r="Z13" s="3" t="inlineStr"/>
-      <c r="AA13" s="3" t="inlineStr"/>
-      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="R13" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="S13" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="T13" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="U13" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="V13" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="W13" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="X13" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Y13" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="Z13" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="AA13" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="AB13" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
       <c r="AC13" s="3" t="inlineStr"/>
       <c r="AD13" s="3" t="inlineStr"/>
       <c r="AE13" s="3" t="inlineStr"/>
@@ -2312,71 +3285,139 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L14" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M14" s="9" t="inlineStr">
         <is>
           <t>停电检修</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="N14" s="9" t="inlineStr">
         <is>
           <t>停电检修</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="O14" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="P14" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I14" s="11" t="inlineStr">
+      <c r="Q14" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="J14" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K14" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr"/>
-      <c r="N14" s="3" t="inlineStr"/>
-      <c r="O14" s="3" t="inlineStr"/>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr"/>
-      <c r="T14" s="3" t="inlineStr"/>
-      <c r="U14" s="3" t="inlineStr"/>
-      <c r="V14" s="3" t="inlineStr"/>
-      <c r="W14" s="3" t="inlineStr"/>
-      <c r="X14" s="3" t="inlineStr"/>
-      <c r="Y14" s="3" t="inlineStr"/>
-      <c r="Z14" s="3" t="inlineStr"/>
-      <c r="AA14" s="3" t="inlineStr"/>
-      <c r="AB14" s="3" t="inlineStr"/>
+      <c r="R14" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="S14" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T14" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U14" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="V14" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="W14" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="X14" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="Y14" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="Z14" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="AA14" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="AB14" s="10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
       <c r="AC14" s="3" t="inlineStr"/>
       <c r="AD14" s="3" t="inlineStr"/>
       <c r="AE14" s="3" t="inlineStr"/>
@@ -2390,71 +3431,139 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L15" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M15" s="9" t="inlineStr">
         <is>
           <t>停电检修</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="N15" s="9" t="inlineStr">
         <is>
           <t>停电检修</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="O15" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="P15" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
+      <c r="Q15" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K15" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr"/>
-      <c r="N15" s="3" t="inlineStr"/>
-      <c r="O15" s="3" t="inlineStr"/>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr"/>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="3" t="inlineStr"/>
-      <c r="T15" s="3" t="inlineStr"/>
-      <c r="U15" s="3" t="inlineStr"/>
-      <c r="V15" s="3" t="inlineStr"/>
-      <c r="W15" s="3" t="inlineStr"/>
-      <c r="X15" s="3" t="inlineStr"/>
-      <c r="Y15" s="3" t="inlineStr"/>
-      <c r="Z15" s="3" t="inlineStr"/>
-      <c r="AA15" s="3" t="inlineStr"/>
-      <c r="AB15" s="3" t="inlineStr"/>
+      <c r="R15" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="S15" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T15" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U15" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="V15" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="W15" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="X15" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y15" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Z15" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AA15" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AB15" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="AC15" s="3" t="inlineStr"/>
       <c r="AD15" s="3" t="inlineStr"/>
       <c r="AE15" s="3" t="inlineStr"/>
@@ -2468,71 +3577,139 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L16" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M16" s="9" t="inlineStr">
         <is>
           <t>停电检修</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="N16" s="9" t="inlineStr">
         <is>
           <t>停电检修</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="O16" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="P16" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I16" s="11" t="inlineStr">
+      <c r="Q16" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="J16" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K16" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr"/>
-      <c r="N16" s="3" t="inlineStr"/>
-      <c r="O16" s="3" t="inlineStr"/>
-      <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr"/>
-      <c r="S16" s="3" t="inlineStr"/>
-      <c r="T16" s="3" t="inlineStr"/>
-      <c r="U16" s="3" t="inlineStr"/>
-      <c r="V16" s="3" t="inlineStr"/>
-      <c r="W16" s="3" t="inlineStr"/>
-      <c r="X16" s="3" t="inlineStr"/>
-      <c r="Y16" s="3" t="inlineStr"/>
-      <c r="Z16" s="3" t="inlineStr"/>
-      <c r="AA16" s="3" t="inlineStr"/>
-      <c r="AB16" s="3" t="inlineStr"/>
+      <c r="R16" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="S16" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T16" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U16" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="V16" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="W16" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="X16" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y16" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Z16" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AA16" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AB16" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="AC16" s="3" t="inlineStr"/>
       <c r="AD16" s="3" t="inlineStr"/>
       <c r="AE16" s="3" t="inlineStr"/>
@@ -2546,71 +3723,139 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L17" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M17" s="9" t="inlineStr">
         <is>
           <t>停电检修</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="N17" s="9" t="inlineStr">
         <is>
           <t>停电检修</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="O17" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="P17" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I17" s="11" t="inlineStr">
+      <c r="Q17" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="J17" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K17" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="3" t="inlineStr"/>
-      <c r="N17" s="3" t="inlineStr"/>
-      <c r="O17" s="3" t="inlineStr"/>
-      <c r="P17" s="3" t="inlineStr"/>
-      <c r="Q17" s="3" t="inlineStr"/>
-      <c r="R17" s="3" t="inlineStr"/>
-      <c r="S17" s="3" t="inlineStr"/>
-      <c r="T17" s="3" t="inlineStr"/>
-      <c r="U17" s="3" t="inlineStr"/>
-      <c r="V17" s="3" t="inlineStr"/>
-      <c r="W17" s="3" t="inlineStr"/>
-      <c r="X17" s="3" t="inlineStr"/>
-      <c r="Y17" s="3" t="inlineStr"/>
-      <c r="Z17" s="3" t="inlineStr"/>
-      <c r="AA17" s="3" t="inlineStr"/>
-      <c r="AB17" s="3" t="inlineStr"/>
+      <c r="R17" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="S17" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T17" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U17" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="V17" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="W17" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="X17" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y17" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Z17" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AA17" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AB17" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="AC17" s="3" t="inlineStr"/>
       <c r="AD17" s="3" t="inlineStr"/>
       <c r="AE17" s="3" t="inlineStr"/>
@@ -2624,71 +3869,139 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J18" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L18" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M18" s="9" t="inlineStr">
         <is>
           <t>停电检修</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="N18" s="9" t="inlineStr">
         <is>
           <t>停电检修</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="O18" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="P18" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I18" s="11" t="inlineStr">
+      <c r="Q18" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="J18" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K18" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr"/>
-      <c r="M18" s="3" t="inlineStr"/>
-      <c r="N18" s="3" t="inlineStr"/>
-      <c r="O18" s="3" t="inlineStr"/>
-      <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="3" t="inlineStr"/>
-      <c r="R18" s="3" t="inlineStr"/>
-      <c r="S18" s="3" t="inlineStr"/>
-      <c r="T18" s="3" t="inlineStr"/>
-      <c r="U18" s="3" t="inlineStr"/>
-      <c r="V18" s="3" t="inlineStr"/>
-      <c r="W18" s="3" t="inlineStr"/>
-      <c r="X18" s="3" t="inlineStr"/>
-      <c r="Y18" s="3" t="inlineStr"/>
-      <c r="Z18" s="3" t="inlineStr"/>
-      <c r="AA18" s="3" t="inlineStr"/>
-      <c r="AB18" s="3" t="inlineStr"/>
+      <c r="R18" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="S18" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T18" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U18" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="V18" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="W18" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="X18" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y18" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Z18" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AA18" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AB18" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="AC18" s="3" t="inlineStr"/>
       <c r="AD18" s="3" t="inlineStr"/>
       <c r="AE18" s="3" t="inlineStr"/>
@@ -2702,71 +4015,139 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J19" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L19" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M19" s="9" t="inlineStr">
         <is>
           <t>停电检修</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="N19" s="9" t="inlineStr">
         <is>
           <t>停电检修</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="O19" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="P19" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr">
+      <c r="Q19" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="J19" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K19" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr"/>
-      <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr"/>
-      <c r="P19" s="3" t="inlineStr"/>
-      <c r="Q19" s="3" t="inlineStr"/>
-      <c r="R19" s="3" t="inlineStr"/>
-      <c r="S19" s="3" t="inlineStr"/>
-      <c r="T19" s="3" t="inlineStr"/>
-      <c r="U19" s="3" t="inlineStr"/>
-      <c r="V19" s="3" t="inlineStr"/>
-      <c r="W19" s="3" t="inlineStr"/>
-      <c r="X19" s="3" t="inlineStr"/>
-      <c r="Y19" s="3" t="inlineStr"/>
-      <c r="Z19" s="3" t="inlineStr"/>
-      <c r="AA19" s="3" t="inlineStr"/>
-      <c r="AB19" s="3" t="inlineStr"/>
+      <c r="R19" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="S19" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T19" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U19" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="V19" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="W19" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="X19" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y19" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Z19" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AA19" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AB19" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="AC19" s="3" t="inlineStr"/>
       <c r="AD19" s="3" t="inlineStr"/>
       <c r="AE19" s="3" t="inlineStr"/>
@@ -2780,71 +4161,139 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J20" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L20" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M20" s="9" t="inlineStr">
         <is>
           <t>停电检修</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="N20" s="9" t="inlineStr">
         <is>
           <t>停电检修</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="O20" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="P20" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I20" s="11" t="inlineStr">
+      <c r="Q20" s="13" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="J20" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K20" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr"/>
-      <c r="M20" s="3" t="inlineStr"/>
-      <c r="N20" s="3" t="inlineStr"/>
-      <c r="O20" s="3" t="inlineStr"/>
-      <c r="P20" s="3" t="inlineStr"/>
-      <c r="Q20" s="3" t="inlineStr"/>
-      <c r="R20" s="3" t="inlineStr"/>
-      <c r="S20" s="3" t="inlineStr"/>
-      <c r="T20" s="3" t="inlineStr"/>
-      <c r="U20" s="3" t="inlineStr"/>
-      <c r="V20" s="3" t="inlineStr"/>
-      <c r="W20" s="3" t="inlineStr"/>
-      <c r="X20" s="3" t="inlineStr"/>
-      <c r="Y20" s="3" t="inlineStr"/>
-      <c r="Z20" s="3" t="inlineStr"/>
-      <c r="AA20" s="3" t="inlineStr"/>
-      <c r="AB20" s="3" t="inlineStr"/>
+      <c r="R20" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="S20" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T20" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U20" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="V20" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="W20" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="X20" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y20" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Z20" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AA20" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AB20" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="AC20" s="3" t="inlineStr"/>
       <c r="AD20" s="3" t="inlineStr"/>
       <c r="AE20" s="3" t="inlineStr"/>
@@ -3021,25 +4470,35 @@
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr"/>
-      <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="3" t="inlineStr"/>
-      <c r="E24" s="3" t="inlineStr"/>
-      <c r="F24" s="3" t="inlineStr"/>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="3" t="inlineStr"/>
+      <c r="B24" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="C24" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="D24" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="F24" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="G24" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="H24" s="16" t="n">
+        <v>230000</v>
+      </c>
       <c r="I24" s="3" t="inlineStr"/>
-      <c r="J24" s="14" t="n">
-        <v>218500</v>
-      </c>
-      <c r="K24" s="14" t="n">
-        <v>230000</v>
-      </c>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
       <c r="N24" s="3" t="inlineStr"/>
@@ -3063,25 +4522,35 @@
       <c r="AF24" s="3" t="inlineStr"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr"/>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="3" t="inlineStr"/>
+      <c r="B25" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="C25" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="D25" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="F25" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="G25" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="H25" s="16" t="n">
+        <v>230000</v>
+      </c>
       <c r="I25" s="3" t="inlineStr"/>
-      <c r="J25" s="14" t="n">
-        <v>218500</v>
-      </c>
-      <c r="K25" s="14" t="n">
-        <v>230000</v>
-      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
       <c r="L25" s="3" t="inlineStr"/>
       <c r="M25" s="3" t="inlineStr"/>
       <c r="N25" s="3" t="inlineStr"/>
@@ -3105,25 +4574,35 @@
       <c r="AF25" s="3" t="inlineStr"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr"/>
-      <c r="C26" s="3" t="inlineStr"/>
-      <c r="D26" s="3" t="inlineStr"/>
-      <c r="E26" s="3" t="inlineStr"/>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="3" t="inlineStr"/>
+      <c r="B26" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="C26" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="D26" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="F26" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="G26" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="H26" s="16" t="n">
+        <v>230000</v>
+      </c>
       <c r="I26" s="3" t="inlineStr"/>
-      <c r="J26" s="14" t="n">
-        <v>218500</v>
-      </c>
-      <c r="K26" s="14" t="n">
-        <v>230000</v>
-      </c>
+      <c r="J26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="inlineStr"/>
       <c r="L26" s="3" t="inlineStr"/>
       <c r="M26" s="3" t="inlineStr"/>
       <c r="N26" s="3" t="inlineStr"/>
@@ -3147,25 +4626,35 @@
       <c r="AF26" s="3" t="inlineStr"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr"/>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="3" t="inlineStr"/>
+      <c r="B27" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="C27" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="D27" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="F27" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="G27" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="H27" s="16" t="n">
+        <v>230000</v>
+      </c>
       <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="14" t="n">
-        <v>218500</v>
-      </c>
-      <c r="K27" s="14" t="n">
-        <v>230000</v>
-      </c>
+      <c r="J27" s="3" t="inlineStr"/>
+      <c r="K27" s="3" t="inlineStr"/>
       <c r="L27" s="3" t="inlineStr"/>
       <c r="M27" s="3" t="inlineStr"/>
       <c r="N27" s="3" t="inlineStr"/>
@@ -3189,25 +4678,35 @@
       <c r="AF27" s="3" t="inlineStr"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr"/>
-      <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="3" t="inlineStr"/>
-      <c r="E28" s="3" t="inlineStr"/>
-      <c r="F28" s="3" t="inlineStr"/>
-      <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="3" t="inlineStr"/>
+      <c r="B28" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="C28" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="D28" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="F28" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="G28" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="H28" s="16" t="n">
+        <v>230000</v>
+      </c>
       <c r="I28" s="3" t="inlineStr"/>
-      <c r="J28" s="14" t="n">
-        <v>218500</v>
-      </c>
-      <c r="K28" s="14" t="n">
-        <v>230000</v>
-      </c>
+      <c r="J28" s="3" t="inlineStr"/>
+      <c r="K28" s="3" t="inlineStr"/>
       <c r="L28" s="3" t="inlineStr"/>
       <c r="M28" s="3" t="inlineStr"/>
       <c r="N28" s="3" t="inlineStr"/>
@@ -3231,25 +4730,35 @@
       <c r="AF28" s="3" t="inlineStr"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr"/>
-      <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr"/>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="3" t="inlineStr"/>
+      <c r="B29" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="C29" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="D29" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="F29" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="G29" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="H29" s="16" t="n">
+        <v>230000</v>
+      </c>
       <c r="I29" s="3" t="inlineStr"/>
-      <c r="J29" s="14" t="n">
-        <v>218500</v>
-      </c>
-      <c r="K29" s="14" t="n">
-        <v>230000</v>
-      </c>
+      <c r="J29" s="3" t="inlineStr"/>
+      <c r="K29" s="3" t="inlineStr"/>
       <c r="L29" s="3" t="inlineStr"/>
       <c r="M29" s="3" t="inlineStr"/>
       <c r="N29" s="3" t="inlineStr"/>
@@ -3273,25 +4782,35 @@
       <c r="AF29" s="3" t="inlineStr"/>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr"/>
-      <c r="C30" s="3" t="inlineStr"/>
-      <c r="D30" s="3" t="inlineStr"/>
-      <c r="E30" s="3" t="inlineStr"/>
-      <c r="F30" s="3" t="inlineStr"/>
-      <c r="G30" s="3" t="inlineStr"/>
-      <c r="H30" s="3" t="inlineStr"/>
+      <c r="B30" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="C30" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="D30" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="F30" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="G30" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="H30" s="16" t="n">
+        <v>230000</v>
+      </c>
       <c r="I30" s="3" t="inlineStr"/>
-      <c r="J30" s="14" t="n">
-        <v>218500</v>
-      </c>
-      <c r="K30" s="14" t="n">
-        <v>230000</v>
-      </c>
+      <c r="J30" s="3" t="inlineStr"/>
+      <c r="K30" s="3" t="inlineStr"/>
       <c r="L30" s="3" t="inlineStr"/>
       <c r="M30" s="3" t="inlineStr"/>
       <c r="N30" s="3" t="inlineStr"/>
@@ -3315,25 +4834,35 @@
       <c r="AF30" s="3" t="inlineStr"/>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr"/>
-      <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr"/>
-      <c r="G31" s="3" t="inlineStr"/>
-      <c r="H31" s="3" t="inlineStr"/>
+      <c r="B31" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="C31" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="D31" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="F31" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="G31" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="H31" s="16" t="n">
+        <v>230000</v>
+      </c>
       <c r="I31" s="3" t="inlineStr"/>
-      <c r="J31" s="14" t="n">
-        <v>218500</v>
-      </c>
-      <c r="K31" s="14" t="n">
-        <v>230000</v>
-      </c>
+      <c r="J31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="inlineStr"/>
       <c r="M31" s="3" t="inlineStr"/>
       <c r="N31" s="3" t="inlineStr"/>
@@ -3357,11 +4886,7 @@
       <c r="AF31" s="3" t="inlineStr"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="A32" s="6" t="inlineStr"/>
       <c r="B32" s="3" t="inlineStr"/>
       <c r="C32" s="3" t="inlineStr"/>
       <c r="D32" s="3" t="inlineStr"/>
@@ -3370,12 +4895,8 @@
       <c r="G32" s="3" t="inlineStr"/>
       <c r="H32" s="3" t="inlineStr"/>
       <c r="I32" s="3" t="inlineStr"/>
-      <c r="J32" s="14" t="n">
-        <v>218500</v>
-      </c>
-      <c r="K32" s="14" t="n">
-        <v>230000</v>
-      </c>
+      <c r="J32" s="3" t="inlineStr"/>
+      <c r="K32" s="3" t="inlineStr"/>
       <c r="L32" s="3" t="inlineStr"/>
       <c r="M32" s="3" t="inlineStr"/>
       <c r="N32" s="3" t="inlineStr"/>
@@ -3399,25 +4920,35 @@
       <c r="AF32" s="3" t="inlineStr"/>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr"/>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr"/>
-      <c r="G33" s="3" t="inlineStr"/>
-      <c r="H33" s="3" t="inlineStr"/>
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="C33" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="D33" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="F33" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="G33" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="H33" s="18" t="n">
+        <v>230000</v>
+      </c>
       <c r="I33" s="3" t="inlineStr"/>
-      <c r="J33" s="14" t="n">
-        <v>218500</v>
-      </c>
-      <c r="K33" s="14" t="n">
-        <v>230000</v>
-      </c>
+      <c r="J33" s="3" t="inlineStr"/>
+      <c r="K33" s="3" t="inlineStr"/>
       <c r="L33" s="3" t="inlineStr"/>
       <c r="M33" s="3" t="inlineStr"/>
       <c r="N33" s="3" t="inlineStr"/>
@@ -3441,25 +4972,35 @@
       <c r="AF33" s="3" t="inlineStr"/>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr"/>
-      <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="3" t="inlineStr"/>
-      <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr"/>
-      <c r="H34" s="3" t="inlineStr"/>
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="C34" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="D34" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="E34" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="F34" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="G34" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="H34" s="18" t="n">
+        <v>230000</v>
+      </c>
       <c r="I34" s="3" t="inlineStr"/>
-      <c r="J34" s="14" t="n">
-        <v>218500</v>
-      </c>
-      <c r="K34" s="14" t="n">
-        <v>230000</v>
-      </c>
+      <c r="J34" s="3" t="inlineStr"/>
+      <c r="K34" s="3" t="inlineStr"/>
       <c r="L34" s="3" t="inlineStr"/>
       <c r="M34" s="3" t="inlineStr"/>
       <c r="N34" s="3" t="inlineStr"/>
@@ -3483,25 +5024,35 @@
       <c r="AF34" s="3" t="inlineStr"/>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr"/>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="3" t="inlineStr"/>
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B35" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="C35" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="D35" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="E35" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="F35" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="G35" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="H35" s="18" t="n">
+        <v>230000</v>
+      </c>
       <c r="I35" s="3" t="inlineStr"/>
-      <c r="J35" s="14" t="n">
-        <v>218500</v>
-      </c>
-      <c r="K35" s="14" t="n">
-        <v>230000</v>
-      </c>
+      <c r="J35" s="3" t="inlineStr"/>
+      <c r="K35" s="3" t="inlineStr"/>
       <c r="L35" s="3" t="inlineStr"/>
       <c r="M35" s="3" t="inlineStr"/>
       <c r="N35" s="3" t="inlineStr"/>
@@ -3525,25 +5076,35 @@
       <c r="AF35" s="3" t="inlineStr"/>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr"/>
-      <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="3" t="inlineStr"/>
-      <c r="E36" s="3" t="inlineStr"/>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr"/>
-      <c r="H36" s="3" t="inlineStr"/>
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="D36" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="F36" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="G36" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="H36" s="18" t="n">
+        <v>230000</v>
+      </c>
       <c r="I36" s="3" t="inlineStr"/>
-      <c r="J36" s="14" t="n">
-        <v>218500</v>
-      </c>
-      <c r="K36" s="14" t="n">
-        <v>230000</v>
-      </c>
+      <c r="J36" s="3" t="inlineStr"/>
+      <c r="K36" s="3" t="inlineStr"/>
       <c r="L36" s="3" t="inlineStr"/>
       <c r="M36" s="3" t="inlineStr"/>
       <c r="N36" s="3" t="inlineStr"/>
@@ -3567,25 +5128,35 @@
       <c r="AF36" s="3" t="inlineStr"/>
     </row>
     <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr"/>
-      <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
-      <c r="H37" s="3" t="inlineStr"/>
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B37" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="C37" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="D37" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="E37" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="F37" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="G37" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="H37" s="18" t="n">
+        <v>230000</v>
+      </c>
       <c r="I37" s="3" t="inlineStr"/>
-      <c r="J37" s="14" t="n">
-        <v>218500</v>
-      </c>
-      <c r="K37" s="14" t="n">
-        <v>230000</v>
-      </c>
+      <c r="J37" s="3" t="inlineStr"/>
+      <c r="K37" s="3" t="inlineStr"/>
       <c r="L37" s="3" t="inlineStr"/>
       <c r="M37" s="3" t="inlineStr"/>
       <c r="N37" s="3" t="inlineStr"/>
@@ -3609,25 +5180,35 @@
       <c r="AF37" s="3" t="inlineStr"/>
     </row>
     <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr"/>
-      <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="3" t="inlineStr"/>
-      <c r="E38" s="3" t="inlineStr"/>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="3" t="inlineStr"/>
-      <c r="H38" s="3" t="inlineStr"/>
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="C38" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="D38" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="E38" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="F38" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="G38" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="H38" s="18" t="n">
+        <v>230000</v>
+      </c>
       <c r="I38" s="3" t="inlineStr"/>
-      <c r="J38" s="14" t="n">
-        <v>218500</v>
-      </c>
-      <c r="K38" s="14" t="n">
-        <v>230000</v>
-      </c>
+      <c r="J38" s="3" t="inlineStr"/>
+      <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="inlineStr"/>
       <c r="M38" s="3" t="inlineStr"/>
       <c r="N38" s="3" t="inlineStr"/>
@@ -3651,25 +5232,35 @@
       <c r="AF38" s="3" t="inlineStr"/>
     </row>
     <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr"/>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="3" t="inlineStr"/>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="3" t="inlineStr"/>
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="C39" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="D39" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="E39" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="F39" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="G39" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="H39" s="18" t="n">
+        <v>230000</v>
+      </c>
       <c r="I39" s="3" t="inlineStr"/>
-      <c r="J39" s="14" t="n">
-        <v>218500</v>
-      </c>
-      <c r="K39" s="14" t="n">
-        <v>230000</v>
-      </c>
+      <c r="J39" s="3" t="inlineStr"/>
+      <c r="K39" s="3" t="inlineStr"/>
       <c r="L39" s="3" t="inlineStr"/>
       <c r="M39" s="3" t="inlineStr"/>
       <c r="N39" s="3" t="inlineStr"/>
@@ -3693,25 +5284,39 @@
       <c r="AF39" s="3" t="inlineStr"/>
     </row>
     <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr"/>
-      <c r="C40" s="3" t="inlineStr"/>
-      <c r="D40" s="3" t="inlineStr"/>
-      <c r="E40" s="3" t="inlineStr"/>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="3" t="inlineStr"/>
-      <c r="I40" s="3" t="inlineStr"/>
-      <c r="J40" s="14" t="n">
-        <v>218500</v>
-      </c>
-      <c r="K40" s="14" t="n">
-        <v>230000</v>
-      </c>
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="C40" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="D40" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="E40" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="F40" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="G40" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="H40" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="I40" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J40" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="K40" s="3" t="inlineStr"/>
       <c r="L40" s="3" t="inlineStr"/>
       <c r="M40" s="3" t="inlineStr"/>
       <c r="N40" s="3" t="inlineStr"/>
@@ -3735,25 +5340,39 @@
       <c r="AF40" s="3" t="inlineStr"/>
     </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr"/>
-      <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="inlineStr"/>
-      <c r="J41" s="14" t="n">
-        <v>218500</v>
-      </c>
-      <c r="K41" s="14" t="n">
-        <v>230000</v>
-      </c>
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B41" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="C41" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="D41" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="E41" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="F41" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="G41" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="H41" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="I41" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J41" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="K41" s="3" t="inlineStr"/>
       <c r="L41" s="3" t="inlineStr"/>
       <c r="M41" s="3" t="inlineStr"/>
       <c r="N41" s="3" t="inlineStr"/>
@@ -3777,16 +5396,38 @@
       <c r="AF41" s="3" t="inlineStr"/>
     </row>
     <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="6" t="inlineStr"/>
-      <c r="B42" s="3" t="inlineStr"/>
-      <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="3" t="inlineStr"/>
-      <c r="E42" s="3" t="inlineStr"/>
-      <c r="F42" s="3" t="inlineStr"/>
-      <c r="G42" s="3" t="inlineStr"/>
-      <c r="H42" s="3" t="inlineStr"/>
-      <c r="I42" s="3" t="inlineStr"/>
-      <c r="J42" s="3" t="inlineStr"/>
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="C42" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="D42" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="E42" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="F42" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="G42" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="H42" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="I42" s="18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J42" s="18" t="n">
+        <v>230000</v>
+      </c>
       <c r="K42" s="3" t="inlineStr"/>
       <c r="L42" s="3" t="inlineStr"/>
       <c r="M42" s="3" t="inlineStr"/>
@@ -3811,31 +5452,15 @@
       <c r="AF42" s="3" t="inlineStr"/>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="n">
-        <v>230000</v>
-      </c>
-      <c r="C43" s="16" t="n">
-        <v>230000</v>
-      </c>
-      <c r="D43" s="16" t="n">
-        <v>180082</v>
-      </c>
+      <c r="A43" s="6" t="inlineStr"/>
+      <c r="B43" s="3" t="inlineStr"/>
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr"/>
       <c r="E43" s="3" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="16" t="n">
-        <v>92000</v>
-      </c>
-      <c r="H43" s="16" t="n">
-        <v>184000</v>
-      </c>
-      <c r="I43" s="16" t="n">
-        <v>207000</v>
-      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr"/>
+      <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
       <c r="K43" s="3" t="inlineStr"/>
       <c r="L43" s="3" t="inlineStr"/>
@@ -3861,46 +5486,62 @@
       <c r="AF43" s="3" t="inlineStr"/>
     </row>
     <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="n">
-        <v>230000</v>
-      </c>
-      <c r="C44" s="16" t="n">
-        <v>230000</v>
-      </c>
-      <c r="D44" s="16" t="n">
-        <v>180082</v>
-      </c>
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr"/>
+      <c r="C44" s="3" t="inlineStr"/>
+      <c r="D44" s="3" t="inlineStr"/>
       <c r="E44" s="3" t="inlineStr"/>
       <c r="F44" s="3" t="inlineStr"/>
-      <c r="G44" s="16" t="n">
-        <v>92000</v>
-      </c>
-      <c r="H44" s="16" t="n">
-        <v>184000</v>
-      </c>
-      <c r="I44" s="16" t="n">
-        <v>207000</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="3" t="inlineStr"/>
-      <c r="L44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J44" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="K44" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="L44" s="20" t="n">
+        <v>153009</v>
+      </c>
       <c r="M44" s="3" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
-      <c r="O44" s="3" t="inlineStr"/>
-      <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="3" t="inlineStr"/>
-      <c r="R44" s="3" t="inlineStr"/>
-      <c r="S44" s="3" t="inlineStr"/>
-      <c r="T44" s="3" t="inlineStr"/>
-      <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="3" t="inlineStr"/>
-      <c r="W44" s="3" t="inlineStr"/>
-      <c r="X44" s="3" t="inlineStr"/>
+      <c r="O44" s="20" t="n">
+        <v>92000</v>
+      </c>
+      <c r="P44" s="20" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q44" s="20" t="n">
+        <v>207000</v>
+      </c>
+      <c r="R44" s="20" t="n">
+        <v>218500</v>
+      </c>
+      <c r="S44" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="T44" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U44" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="V44" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="W44" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="X44" s="20" t="n">
+        <v>230000</v>
+      </c>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
       <c r="AA44" s="3" t="inlineStr"/>
@@ -3911,46 +5552,62 @@
       <c r="AF44" s="3" t="inlineStr"/>
     </row>
     <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="n">
-        <v>230000</v>
-      </c>
-      <c r="C45" s="16" t="n">
-        <v>230000</v>
-      </c>
-      <c r="D45" s="16" t="n">
-        <v>180082</v>
-      </c>
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr"/>
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr"/>
       <c r="E45" s="3" t="inlineStr"/>
       <c r="F45" s="3" t="inlineStr"/>
-      <c r="G45" s="16" t="n">
-        <v>92000</v>
-      </c>
-      <c r="H45" s="16" t="n">
-        <v>184000</v>
-      </c>
-      <c r="I45" s="16" t="n">
-        <v>207000</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr"/>
-      <c r="K45" s="3" t="inlineStr"/>
-      <c r="L45" s="3" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr"/>
+      <c r="I45" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J45" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="K45" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="L45" s="20" t="n">
+        <v>153009</v>
+      </c>
       <c r="M45" s="3" t="inlineStr"/>
       <c r="N45" s="3" t="inlineStr"/>
-      <c r="O45" s="3" t="inlineStr"/>
-      <c r="P45" s="3" t="inlineStr"/>
-      <c r="Q45" s="3" t="inlineStr"/>
-      <c r="R45" s="3" t="inlineStr"/>
-      <c r="S45" s="3" t="inlineStr"/>
-      <c r="T45" s="3" t="inlineStr"/>
-      <c r="U45" s="3" t="inlineStr"/>
-      <c r="V45" s="3" t="inlineStr"/>
-      <c r="W45" s="3" t="inlineStr"/>
-      <c r="X45" s="3" t="inlineStr"/>
+      <c r="O45" s="20" t="n">
+        <v>92000</v>
+      </c>
+      <c r="P45" s="20" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q45" s="20" t="n">
+        <v>207000</v>
+      </c>
+      <c r="R45" s="20" t="n">
+        <v>218500</v>
+      </c>
+      <c r="S45" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="T45" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U45" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="V45" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="W45" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="X45" s="20" t="n">
+        <v>230000</v>
+      </c>
       <c r="Y45" s="3" t="inlineStr"/>
       <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr"/>
@@ -3961,46 +5618,62 @@
       <c r="AF45" s="3" t="inlineStr"/>
     </row>
     <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="n">
-        <v>230000</v>
-      </c>
-      <c r="C46" s="16" t="n">
-        <v>230000</v>
-      </c>
-      <c r="D46" s="16" t="n">
-        <v>180082</v>
-      </c>
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr"/>
+      <c r="C46" s="3" t="inlineStr"/>
+      <c r="D46" s="3" t="inlineStr"/>
       <c r="E46" s="3" t="inlineStr"/>
       <c r="F46" s="3" t="inlineStr"/>
-      <c r="G46" s="16" t="n">
-        <v>92000</v>
-      </c>
-      <c r="H46" s="16" t="n">
-        <v>184000</v>
-      </c>
-      <c r="I46" s="16" t="n">
-        <v>207000</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr"/>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="3" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr"/>
+      <c r="I46" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J46" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="K46" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="L46" s="20" t="n">
+        <v>153009</v>
+      </c>
       <c r="M46" s="3" t="inlineStr"/>
       <c r="N46" s="3" t="inlineStr"/>
-      <c r="O46" s="3" t="inlineStr"/>
-      <c r="P46" s="3" t="inlineStr"/>
-      <c r="Q46" s="3" t="inlineStr"/>
-      <c r="R46" s="3" t="inlineStr"/>
-      <c r="S46" s="3" t="inlineStr"/>
-      <c r="T46" s="3" t="inlineStr"/>
-      <c r="U46" s="3" t="inlineStr"/>
-      <c r="V46" s="3" t="inlineStr"/>
-      <c r="W46" s="3" t="inlineStr"/>
-      <c r="X46" s="3" t="inlineStr"/>
+      <c r="O46" s="20" t="n">
+        <v>92000</v>
+      </c>
+      <c r="P46" s="20" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q46" s="20" t="n">
+        <v>207000</v>
+      </c>
+      <c r="R46" s="20" t="n">
+        <v>218500</v>
+      </c>
+      <c r="S46" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="T46" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U46" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="V46" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="W46" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="X46" s="20" t="n">
+        <v>230000</v>
+      </c>
       <c r="Y46" s="3" t="inlineStr"/>
       <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr"/>
@@ -4011,46 +5684,62 @@
       <c r="AF46" s="3" t="inlineStr"/>
     </row>
     <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B47" s="16" t="n">
-        <v>230000</v>
-      </c>
-      <c r="C47" s="16" t="n">
-        <v>230000</v>
-      </c>
-      <c r="D47" s="16" t="n">
-        <v>180082</v>
-      </c>
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr"/>
+      <c r="C47" s="3" t="inlineStr"/>
+      <c r="D47" s="3" t="inlineStr"/>
       <c r="E47" s="3" t="inlineStr"/>
       <c r="F47" s="3" t="inlineStr"/>
-      <c r="G47" s="16" t="n">
-        <v>92000</v>
-      </c>
-      <c r="H47" s="16" t="n">
-        <v>184000</v>
-      </c>
-      <c r="I47" s="16" t="n">
-        <v>207000</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr"/>
-      <c r="K47" s="3" t="inlineStr"/>
-      <c r="L47" s="3" t="inlineStr"/>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr"/>
+      <c r="I47" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J47" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="K47" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="L47" s="20" t="n">
+        <v>153009</v>
+      </c>
       <c r="M47" s="3" t="inlineStr"/>
       <c r="N47" s="3" t="inlineStr"/>
-      <c r="O47" s="3" t="inlineStr"/>
-      <c r="P47" s="3" t="inlineStr"/>
-      <c r="Q47" s="3" t="inlineStr"/>
-      <c r="R47" s="3" t="inlineStr"/>
-      <c r="S47" s="3" t="inlineStr"/>
-      <c r="T47" s="3" t="inlineStr"/>
-      <c r="U47" s="3" t="inlineStr"/>
-      <c r="V47" s="3" t="inlineStr"/>
-      <c r="W47" s="3" t="inlineStr"/>
-      <c r="X47" s="3" t="inlineStr"/>
+      <c r="O47" s="20" t="n">
+        <v>92000</v>
+      </c>
+      <c r="P47" s="20" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q47" s="20" t="n">
+        <v>207000</v>
+      </c>
+      <c r="R47" s="20" t="n">
+        <v>218500</v>
+      </c>
+      <c r="S47" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="T47" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U47" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="V47" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="W47" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="X47" s="20" t="n">
+        <v>230000</v>
+      </c>
       <c r="Y47" s="3" t="inlineStr"/>
       <c r="Z47" s="3" t="inlineStr"/>
       <c r="AA47" s="3" t="inlineStr"/>
@@ -4061,46 +5750,62 @@
       <c r="AF47" s="3" t="inlineStr"/>
     </row>
     <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="n">
-        <v>230000</v>
-      </c>
-      <c r="C48" s="16" t="n">
-        <v>230000</v>
-      </c>
-      <c r="D48" s="16" t="n">
-        <v>180082</v>
-      </c>
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr"/>
+      <c r="C48" s="3" t="inlineStr"/>
+      <c r="D48" s="3" t="inlineStr"/>
       <c r="E48" s="3" t="inlineStr"/>
       <c r="F48" s="3" t="inlineStr"/>
-      <c r="G48" s="16" t="n">
-        <v>92000</v>
-      </c>
-      <c r="H48" s="16" t="n">
-        <v>184000</v>
-      </c>
-      <c r="I48" s="16" t="n">
-        <v>207000</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr"/>
-      <c r="K48" s="3" t="inlineStr"/>
-      <c r="L48" s="3" t="inlineStr"/>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr"/>
+      <c r="I48" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J48" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="K48" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="L48" s="20" t="n">
+        <v>153009</v>
+      </c>
       <c r="M48" s="3" t="inlineStr"/>
       <c r="N48" s="3" t="inlineStr"/>
-      <c r="O48" s="3" t="inlineStr"/>
-      <c r="P48" s="3" t="inlineStr"/>
-      <c r="Q48" s="3" t="inlineStr"/>
-      <c r="R48" s="3" t="inlineStr"/>
-      <c r="S48" s="3" t="inlineStr"/>
-      <c r="T48" s="3" t="inlineStr"/>
-      <c r="U48" s="3" t="inlineStr"/>
-      <c r="V48" s="3" t="inlineStr"/>
-      <c r="W48" s="3" t="inlineStr"/>
-      <c r="X48" s="3" t="inlineStr"/>
+      <c r="O48" s="20" t="n">
+        <v>92000</v>
+      </c>
+      <c r="P48" s="20" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q48" s="20" t="n">
+        <v>207000</v>
+      </c>
+      <c r="R48" s="20" t="n">
+        <v>218500</v>
+      </c>
+      <c r="S48" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="T48" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U48" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="V48" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="W48" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="X48" s="20" t="n">
+        <v>230000</v>
+      </c>
       <c r="Y48" s="3" t="inlineStr"/>
       <c r="Z48" s="3" t="inlineStr"/>
       <c r="AA48" s="3" t="inlineStr"/>
@@ -4111,7 +5816,11 @@
       <c r="AF48" s="3" t="inlineStr"/>
     </row>
     <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="6" t="inlineStr"/>
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="B49" s="3" t="inlineStr"/>
       <c r="C49" s="3" t="inlineStr"/>
       <c r="D49" s="3" t="inlineStr"/>
@@ -4119,22 +5828,50 @@
       <c r="F49" s="3" t="inlineStr"/>
       <c r="G49" s="3" t="inlineStr"/>
       <c r="H49" s="3" t="inlineStr"/>
-      <c r="I49" s="3" t="inlineStr"/>
-      <c r="J49" s="3" t="inlineStr"/>
-      <c r="K49" s="3" t="inlineStr"/>
-      <c r="L49" s="3" t="inlineStr"/>
+      <c r="I49" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J49" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="K49" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="L49" s="20" t="n">
+        <v>153009</v>
+      </c>
       <c r="M49" s="3" t="inlineStr"/>
       <c r="N49" s="3" t="inlineStr"/>
-      <c r="O49" s="3" t="inlineStr"/>
-      <c r="P49" s="3" t="inlineStr"/>
-      <c r="Q49" s="3" t="inlineStr"/>
-      <c r="R49" s="3" t="inlineStr"/>
-      <c r="S49" s="3" t="inlineStr"/>
-      <c r="T49" s="3" t="inlineStr"/>
-      <c r="U49" s="3" t="inlineStr"/>
-      <c r="V49" s="3" t="inlineStr"/>
-      <c r="W49" s="3" t="inlineStr"/>
-      <c r="X49" s="3" t="inlineStr"/>
+      <c r="O49" s="20" t="n">
+        <v>92000</v>
+      </c>
+      <c r="P49" s="20" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q49" s="20" t="n">
+        <v>207000</v>
+      </c>
+      <c r="R49" s="20" t="n">
+        <v>218500</v>
+      </c>
+      <c r="S49" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="T49" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U49" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="V49" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="W49" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="X49" s="20" t="n">
+        <v>230000</v>
+      </c>
       <c r="Y49" s="3" t="inlineStr"/>
       <c r="Z49" s="3" t="inlineStr"/>
       <c r="AA49" s="3" t="inlineStr"/>
@@ -4145,35 +5882,47 @@
       <c r="AF49" s="3" t="inlineStr"/>
     </row>
     <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B50" s="18" t="n">
-        <v>230000</v>
-      </c>
-      <c r="C50" s="18" t="n">
-        <v>230000</v>
-      </c>
-      <c r="D50" s="18" t="n">
-        <v>180082</v>
-      </c>
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr"/>
+      <c r="C50" s="3" t="inlineStr"/>
+      <c r="D50" s="3" t="inlineStr"/>
       <c r="E50" s="3" t="inlineStr"/>
       <c r="F50" s="3" t="inlineStr"/>
       <c r="G50" s="3" t="inlineStr"/>
       <c r="H50" s="3" t="inlineStr"/>
-      <c r="I50" s="3" t="inlineStr"/>
-      <c r="J50" s="3" t="inlineStr"/>
-      <c r="K50" s="3" t="inlineStr"/>
-      <c r="L50" s="3" t="inlineStr"/>
+      <c r="I50" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J50" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="K50" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="L50" s="20" t="n">
+        <v>153009</v>
+      </c>
       <c r="M50" s="3" t="inlineStr"/>
       <c r="N50" s="3" t="inlineStr"/>
-      <c r="O50" s="3" t="inlineStr"/>
-      <c r="P50" s="3" t="inlineStr"/>
-      <c r="Q50" s="3" t="inlineStr"/>
-      <c r="R50" s="3" t="inlineStr"/>
-      <c r="S50" s="3" t="inlineStr"/>
+      <c r="O50" s="20" t="n">
+        <v>92000</v>
+      </c>
+      <c r="P50" s="20" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q50" s="20" t="n">
+        <v>207000</v>
+      </c>
+      <c r="R50" s="20" t="n">
+        <v>218500</v>
+      </c>
+      <c r="S50" s="20" t="n">
+        <v>230000</v>
+      </c>
       <c r="T50" s="3" t="inlineStr"/>
       <c r="U50" s="3" t="inlineStr"/>
       <c r="V50" s="3" t="inlineStr"/>
@@ -4189,32 +5938,38 @@
       <c r="AF50" s="3" t="inlineStr"/>
     </row>
     <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B51" s="18" t="n">
-        <v>230000</v>
-      </c>
-      <c r="C51" s="18" t="n">
-        <v>230000</v>
-      </c>
-      <c r="D51" s="18" t="n">
-        <v>180082</v>
-      </c>
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr"/>
+      <c r="C51" s="3" t="inlineStr"/>
+      <c r="D51" s="3" t="inlineStr"/>
       <c r="E51" s="3" t="inlineStr"/>
       <c r="F51" s="3" t="inlineStr"/>
       <c r="G51" s="3" t="inlineStr"/>
       <c r="H51" s="3" t="inlineStr"/>
-      <c r="I51" s="3" t="inlineStr"/>
-      <c r="J51" s="3" t="inlineStr"/>
-      <c r="K51" s="3" t="inlineStr"/>
-      <c r="L51" s="3" t="inlineStr"/>
+      <c r="I51" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J51" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="K51" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="L51" s="20" t="n">
+        <v>153009</v>
+      </c>
       <c r="M51" s="3" t="inlineStr"/>
       <c r="N51" s="3" t="inlineStr"/>
-      <c r="O51" s="3" t="inlineStr"/>
-      <c r="P51" s="3" t="inlineStr"/>
+      <c r="O51" s="20" t="n">
+        <v>92000</v>
+      </c>
+      <c r="P51" s="20" t="n">
+        <v>184000</v>
+      </c>
       <c r="Q51" s="3" t="inlineStr"/>
       <c r="R51" s="3" t="inlineStr"/>
       <c r="S51" s="3" t="inlineStr"/>
@@ -4233,28 +5988,30 @@
       <c r="AF51" s="3" t="inlineStr"/>
     </row>
     <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B52" s="18" t="n">
-        <v>230000</v>
-      </c>
-      <c r="C52" s="18" t="n">
-        <v>230000</v>
-      </c>
-      <c r="D52" s="18" t="n">
-        <v>180082</v>
-      </c>
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr"/>
+      <c r="C52" s="3" t="inlineStr"/>
+      <c r="D52" s="3" t="inlineStr"/>
       <c r="E52" s="3" t="inlineStr"/>
       <c r="F52" s="3" t="inlineStr"/>
       <c r="G52" s="3" t="inlineStr"/>
       <c r="H52" s="3" t="inlineStr"/>
-      <c r="I52" s="3" t="inlineStr"/>
-      <c r="J52" s="3" t="inlineStr"/>
-      <c r="K52" s="3" t="inlineStr"/>
-      <c r="L52" s="3" t="inlineStr"/>
+      <c r="I52" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J52" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="K52" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="L52" s="20" t="n">
+        <v>153009</v>
+      </c>
       <c r="M52" s="3" t="inlineStr"/>
       <c r="N52" s="3" t="inlineStr"/>
       <c r="O52" s="3" t="inlineStr"/>
@@ -4277,28 +6034,30 @@
       <c r="AF52" s="3" t="inlineStr"/>
     </row>
     <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B53" s="18" t="n">
-        <v>230000</v>
-      </c>
-      <c r="C53" s="18" t="n">
-        <v>230000</v>
-      </c>
-      <c r="D53" s="18" t="n">
-        <v>180082</v>
-      </c>
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr"/>
+      <c r="C53" s="3" t="inlineStr"/>
+      <c r="D53" s="3" t="inlineStr"/>
       <c r="E53" s="3" t="inlineStr"/>
       <c r="F53" s="3" t="inlineStr"/>
       <c r="G53" s="3" t="inlineStr"/>
       <c r="H53" s="3" t="inlineStr"/>
-      <c r="I53" s="3" t="inlineStr"/>
-      <c r="J53" s="3" t="inlineStr"/>
-      <c r="K53" s="3" t="inlineStr"/>
-      <c r="L53" s="3" t="inlineStr"/>
+      <c r="I53" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J53" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="K53" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="L53" s="20" t="n">
+        <v>153009</v>
+      </c>
       <c r="M53" s="3" t="inlineStr"/>
       <c r="N53" s="3" t="inlineStr"/>
       <c r="O53" s="3" t="inlineStr"/>
@@ -4321,28 +6080,30 @@
       <c r="AF53" s="3" t="inlineStr"/>
     </row>
     <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B54" s="18" t="n">
-        <v>230000</v>
-      </c>
-      <c r="C54" s="18" t="n">
-        <v>230000</v>
-      </c>
-      <c r="D54" s="18" t="n">
-        <v>180082</v>
-      </c>
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr"/>
+      <c r="C54" s="3" t="inlineStr"/>
+      <c r="D54" s="3" t="inlineStr"/>
       <c r="E54" s="3" t="inlineStr"/>
       <c r="F54" s="3" t="inlineStr"/>
       <c r="G54" s="3" t="inlineStr"/>
       <c r="H54" s="3" t="inlineStr"/>
-      <c r="I54" s="3" t="inlineStr"/>
-      <c r="J54" s="3" t="inlineStr"/>
-      <c r="K54" s="3" t="inlineStr"/>
-      <c r="L54" s="3" t="inlineStr"/>
+      <c r="I54" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J54" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="K54" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="L54" s="20" t="n">
+        <v>153009</v>
+      </c>
       <c r="M54" s="3" t="inlineStr"/>
       <c r="N54" s="3" t="inlineStr"/>
       <c r="O54" s="3" t="inlineStr"/>
@@ -4365,27 +6126,27 @@
       <c r="AF54" s="3" t="inlineStr"/>
     </row>
     <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B55" s="18" t="n">
-        <v>230000</v>
-      </c>
-      <c r="C55" s="18" t="n">
-        <v>230000</v>
-      </c>
-      <c r="D55" s="18" t="n">
-        <v>180082</v>
-      </c>
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr"/>
+      <c r="C55" s="3" t="inlineStr"/>
+      <c r="D55" s="3" t="inlineStr"/>
       <c r="E55" s="3" t="inlineStr"/>
       <c r="F55" s="3" t="inlineStr"/>
       <c r="G55" s="3" t="inlineStr"/>
       <c r="H55" s="3" t="inlineStr"/>
-      <c r="I55" s="3" t="inlineStr"/>
-      <c r="J55" s="3" t="inlineStr"/>
-      <c r="K55" s="3" t="inlineStr"/>
+      <c r="I55" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J55" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="K55" s="20" t="n">
+        <v>230000</v>
+      </c>
       <c r="L55" s="3" t="inlineStr"/>
       <c r="M55" s="3" t="inlineStr"/>
       <c r="N55" s="3" t="inlineStr"/>
@@ -4409,26 +6170,24 @@
       <c r="AF55" s="3" t="inlineStr"/>
     </row>
     <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B56" s="18" t="n">
-        <v>230000</v>
-      </c>
-      <c r="C56" s="18" t="n">
-        <v>230000</v>
-      </c>
-      <c r="D56" s="18" t="n">
-        <v>180082</v>
-      </c>
+      <c r="A56" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr"/>
+      <c r="C56" s="3" t="inlineStr"/>
+      <c r="D56" s="3" t="inlineStr"/>
       <c r="E56" s="3" t="inlineStr"/>
       <c r="F56" s="3" t="inlineStr"/>
       <c r="G56" s="3" t="inlineStr"/>
       <c r="H56" s="3" t="inlineStr"/>
-      <c r="I56" s="3" t="inlineStr"/>
-      <c r="J56" s="3" t="inlineStr"/>
+      <c r="I56" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J56" s="20" t="n">
+        <v>230000</v>
+      </c>
       <c r="K56" s="3" t="inlineStr"/>
       <c r="L56" s="3" t="inlineStr"/>
       <c r="M56" s="3" t="inlineStr"/>
@@ -4453,7 +6212,11 @@
       <c r="AF56" s="3" t="inlineStr"/>
     </row>
     <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="6" t="inlineStr"/>
+      <c r="A57" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="B57" s="3" t="inlineStr"/>
       <c r="C57" s="3" t="inlineStr"/>
       <c r="D57" s="3" t="inlineStr"/>
@@ -4461,8 +6224,12 @@
       <c r="F57" s="3" t="inlineStr"/>
       <c r="G57" s="3" t="inlineStr"/>
       <c r="H57" s="3" t="inlineStr"/>
-      <c r="I57" s="3" t="inlineStr"/>
-      <c r="J57" s="3" t="inlineStr"/>
+      <c r="I57" s="20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J57" s="20" t="n">
+        <v>230000</v>
+      </c>
       <c r="K57" s="3" t="inlineStr"/>
       <c r="L57" s="3" t="inlineStr"/>
       <c r="M57" s="3" t="inlineStr"/>
@@ -4489,7 +6256,7 @@
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="19" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr"/>
@@ -4497,16 +6264,14 @@
       <c r="D58" s="3" t="inlineStr"/>
       <c r="E58" s="3" t="inlineStr"/>
       <c r="F58" s="3" t="inlineStr"/>
-      <c r="G58" s="20" t="n">
-        <v>92000</v>
-      </c>
-      <c r="H58" s="20" t="n">
-        <v>184000</v>
-      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr"/>
       <c r="I58" s="20" t="n">
-        <v>207000</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr"/>
+        <v>230000</v>
+      </c>
+      <c r="J58" s="20" t="n">
+        <v>230000</v>
+      </c>
       <c r="K58" s="3" t="inlineStr"/>
       <c r="L58" s="3" t="inlineStr"/>
       <c r="M58" s="3" t="inlineStr"/>
@@ -4531,25 +6296,15 @@
       <c r="AF58" s="3" t="inlineStr"/>
     </row>
     <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
+      <c r="A59" s="6" t="inlineStr"/>
       <c r="B59" s="3" t="inlineStr"/>
       <c r="C59" s="3" t="inlineStr"/>
       <c r="D59" s="3" t="inlineStr"/>
       <c r="E59" s="3" t="inlineStr"/>
       <c r="F59" s="3" t="inlineStr"/>
-      <c r="G59" s="20" t="n">
-        <v>92000</v>
-      </c>
-      <c r="H59" s="20" t="n">
-        <v>184000</v>
-      </c>
-      <c r="I59" s="20" t="n">
-        <v>207000</v>
-      </c>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr"/>
+      <c r="I59" s="3" t="inlineStr"/>
       <c r="J59" s="3" t="inlineStr"/>
       <c r="K59" s="3" t="inlineStr"/>
       <c r="L59" s="3" t="inlineStr"/>
@@ -4575,7 +6330,7 @@
       <c r="AF59" s="3" t="inlineStr"/>
     </row>
     <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="19" t="inlineStr">
+      <c r="A60" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4585,28 +6340,40 @@
       <c r="D60" s="3" t="inlineStr"/>
       <c r="E60" s="3" t="inlineStr"/>
       <c r="F60" s="3" t="inlineStr"/>
-      <c r="G60" s="20" t="n">
-        <v>92000</v>
-      </c>
-      <c r="H60" s="20" t="n">
-        <v>184000</v>
-      </c>
-      <c r="I60" s="20" t="n">
-        <v>207000</v>
-      </c>
+      <c r="G60" s="3" t="inlineStr"/>
+      <c r="H60" s="3" t="inlineStr"/>
+      <c r="I60" s="3" t="inlineStr"/>
       <c r="J60" s="3" t="inlineStr"/>
       <c r="K60" s="3" t="inlineStr"/>
-      <c r="L60" s="3" t="inlineStr"/>
+      <c r="L60" s="22" t="n">
+        <v>153009</v>
+      </c>
       <c r="M60" s="3" t="inlineStr"/>
       <c r="N60" s="3" t="inlineStr"/>
-      <c r="O60" s="3" t="inlineStr"/>
-      <c r="P60" s="3" t="inlineStr"/>
-      <c r="Q60" s="3" t="inlineStr"/>
-      <c r="R60" s="3" t="inlineStr"/>
-      <c r="S60" s="3" t="inlineStr"/>
-      <c r="T60" s="3" t="inlineStr"/>
-      <c r="U60" s="3" t="inlineStr"/>
-      <c r="V60" s="3" t="inlineStr"/>
+      <c r="O60" s="22" t="n">
+        <v>92000</v>
+      </c>
+      <c r="P60" s="22" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q60" s="22" t="n">
+        <v>207000</v>
+      </c>
+      <c r="R60" s="22" t="n">
+        <v>218500</v>
+      </c>
+      <c r="S60" s="22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="T60" s="22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U60" s="22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="V60" s="22" t="n">
+        <v>230000</v>
+      </c>
       <c r="W60" s="3" t="inlineStr"/>
       <c r="X60" s="3" t="inlineStr"/>
       <c r="Y60" s="3" t="inlineStr"/>
@@ -4619,7 +6386,7 @@
       <c r="AF60" s="3" t="inlineStr"/>
     </row>
     <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="19" t="inlineStr">
+      <c r="A61" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4629,28 +6396,42 @@
       <c r="D61" s="3" t="inlineStr"/>
       <c r="E61" s="3" t="inlineStr"/>
       <c r="F61" s="3" t="inlineStr"/>
-      <c r="G61" s="20" t="n">
-        <v>92000</v>
-      </c>
-      <c r="H61" s="20" t="n">
-        <v>184000</v>
-      </c>
-      <c r="I61" s="20" t="n">
-        <v>207000</v>
-      </c>
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="3" t="inlineStr"/>
+      <c r="I61" s="3" t="inlineStr"/>
       <c r="J61" s="3" t="inlineStr"/>
-      <c r="K61" s="3" t="inlineStr"/>
-      <c r="L61" s="3" t="inlineStr"/>
+      <c r="K61" s="22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="L61" s="22" t="n">
+        <v>153009</v>
+      </c>
       <c r="M61" s="3" t="inlineStr"/>
       <c r="N61" s="3" t="inlineStr"/>
-      <c r="O61" s="3" t="inlineStr"/>
-      <c r="P61" s="3" t="inlineStr"/>
-      <c r="Q61" s="3" t="inlineStr"/>
-      <c r="R61" s="3" t="inlineStr"/>
-      <c r="S61" s="3" t="inlineStr"/>
-      <c r="T61" s="3" t="inlineStr"/>
-      <c r="U61" s="3" t="inlineStr"/>
-      <c r="V61" s="3" t="inlineStr"/>
+      <c r="O61" s="22" t="n">
+        <v>92000</v>
+      </c>
+      <c r="P61" s="22" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q61" s="22" t="n">
+        <v>207000</v>
+      </c>
+      <c r="R61" s="22" t="n">
+        <v>218500</v>
+      </c>
+      <c r="S61" s="22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="T61" s="22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U61" s="22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="V61" s="22" t="n">
+        <v>230000</v>
+      </c>
       <c r="W61" s="3" t="inlineStr"/>
       <c r="X61" s="3" t="inlineStr"/>
       <c r="Y61" s="3" t="inlineStr"/>
@@ -4663,7 +6444,7 @@
       <c r="AF61" s="3" t="inlineStr"/>
     </row>
     <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="19" t="inlineStr">
+      <c r="A62" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4673,28 +6454,42 @@
       <c r="D62" s="3" t="inlineStr"/>
       <c r="E62" s="3" t="inlineStr"/>
       <c r="F62" s="3" t="inlineStr"/>
-      <c r="G62" s="20" t="n">
-        <v>92000</v>
-      </c>
-      <c r="H62" s="20" t="n">
-        <v>184000</v>
-      </c>
-      <c r="I62" s="20" t="n">
-        <v>207000</v>
-      </c>
+      <c r="G62" s="3" t="inlineStr"/>
+      <c r="H62" s="3" t="inlineStr"/>
+      <c r="I62" s="3" t="inlineStr"/>
       <c r="J62" s="3" t="inlineStr"/>
-      <c r="K62" s="3" t="inlineStr"/>
-      <c r="L62" s="3" t="inlineStr"/>
+      <c r="K62" s="22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="L62" s="22" t="n">
+        <v>153009</v>
+      </c>
       <c r="M62" s="3" t="inlineStr"/>
       <c r="N62" s="3" t="inlineStr"/>
-      <c r="O62" s="3" t="inlineStr"/>
-      <c r="P62" s="3" t="inlineStr"/>
-      <c r="Q62" s="3" t="inlineStr"/>
-      <c r="R62" s="3" t="inlineStr"/>
-      <c r="S62" s="3" t="inlineStr"/>
-      <c r="T62" s="3" t="inlineStr"/>
-      <c r="U62" s="3" t="inlineStr"/>
-      <c r="V62" s="3" t="inlineStr"/>
+      <c r="O62" s="22" t="n">
+        <v>92000</v>
+      </c>
+      <c r="P62" s="22" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q62" s="22" t="n">
+        <v>207000</v>
+      </c>
+      <c r="R62" s="22" t="n">
+        <v>218500</v>
+      </c>
+      <c r="S62" s="22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="T62" s="22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U62" s="22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="V62" s="22" t="n">
+        <v>230000</v>
+      </c>
       <c r="W62" s="3" t="inlineStr"/>
       <c r="X62" s="3" t="inlineStr"/>
       <c r="Y62" s="3" t="inlineStr"/>
@@ -4707,7 +6502,7 @@
       <c r="AF62" s="3" t="inlineStr"/>
     </row>
     <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="19" t="inlineStr">
+      <c r="A63" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4717,28 +6512,42 @@
       <c r="D63" s="3" t="inlineStr"/>
       <c r="E63" s="3" t="inlineStr"/>
       <c r="F63" s="3" t="inlineStr"/>
-      <c r="G63" s="20" t="n">
-        <v>92000</v>
-      </c>
-      <c r="H63" s="20" t="n">
-        <v>184000</v>
-      </c>
-      <c r="I63" s="20" t="n">
-        <v>207000</v>
-      </c>
+      <c r="G63" s="3" t="inlineStr"/>
+      <c r="H63" s="3" t="inlineStr"/>
+      <c r="I63" s="3" t="inlineStr"/>
       <c r="J63" s="3" t="inlineStr"/>
-      <c r="K63" s="3" t="inlineStr"/>
-      <c r="L63" s="3" t="inlineStr"/>
+      <c r="K63" s="22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="L63" s="22" t="n">
+        <v>153009</v>
+      </c>
       <c r="M63" s="3" t="inlineStr"/>
       <c r="N63" s="3" t="inlineStr"/>
-      <c r="O63" s="3" t="inlineStr"/>
-      <c r="P63" s="3" t="inlineStr"/>
-      <c r="Q63" s="3" t="inlineStr"/>
-      <c r="R63" s="3" t="inlineStr"/>
-      <c r="S63" s="3" t="inlineStr"/>
-      <c r="T63" s="3" t="inlineStr"/>
-      <c r="U63" s="3" t="inlineStr"/>
-      <c r="V63" s="3" t="inlineStr"/>
+      <c r="O63" s="22" t="n">
+        <v>92000</v>
+      </c>
+      <c r="P63" s="22" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q63" s="22" t="n">
+        <v>207000</v>
+      </c>
+      <c r="R63" s="22" t="n">
+        <v>218500</v>
+      </c>
+      <c r="S63" s="22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="T63" s="22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U63" s="22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="V63" s="22" t="n">
+        <v>230000</v>
+      </c>
       <c r="W63" s="3" t="inlineStr"/>
       <c r="X63" s="3" t="inlineStr"/>
       <c r="Y63" s="3" t="inlineStr"/>
@@ -4751,7 +6560,7 @@
       <c r="AF63" s="3" t="inlineStr"/>
     </row>
     <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="19" t="inlineStr">
+      <c r="A64" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4761,28 +6570,42 @@
       <c r="D64" s="3" t="inlineStr"/>
       <c r="E64" s="3" t="inlineStr"/>
       <c r="F64" s="3" t="inlineStr"/>
-      <c r="G64" s="20" t="n">
-        <v>92000</v>
-      </c>
-      <c r="H64" s="20" t="n">
-        <v>184000</v>
-      </c>
-      <c r="I64" s="20" t="n">
-        <v>207000</v>
-      </c>
+      <c r="G64" s="3" t="inlineStr"/>
+      <c r="H64" s="3" t="inlineStr"/>
+      <c r="I64" s="3" t="inlineStr"/>
       <c r="J64" s="3" t="inlineStr"/>
-      <c r="K64" s="3" t="inlineStr"/>
-      <c r="L64" s="3" t="inlineStr"/>
+      <c r="K64" s="22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="L64" s="22" t="n">
+        <v>153009</v>
+      </c>
       <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="3" t="inlineStr"/>
-      <c r="O64" s="3" t="inlineStr"/>
-      <c r="P64" s="3" t="inlineStr"/>
-      <c r="Q64" s="3" t="inlineStr"/>
-      <c r="R64" s="3" t="inlineStr"/>
-      <c r="S64" s="3" t="inlineStr"/>
-      <c r="T64" s="3" t="inlineStr"/>
-      <c r="U64" s="3" t="inlineStr"/>
-      <c r="V64" s="3" t="inlineStr"/>
+      <c r="O64" s="22" t="n">
+        <v>92000</v>
+      </c>
+      <c r="P64" s="22" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q64" s="22" t="n">
+        <v>207000</v>
+      </c>
+      <c r="R64" s="22" t="n">
+        <v>218500</v>
+      </c>
+      <c r="S64" s="22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="T64" s="22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U64" s="22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="V64" s="22" t="n">
+        <v>230000</v>
+      </c>
       <c r="W64" s="3" t="inlineStr"/>
       <c r="X64" s="3" t="inlineStr"/>
       <c r="Y64" s="3" t="inlineStr"/>
@@ -4795,7 +6618,7 @@
       <c r="AF64" s="3" t="inlineStr"/>
     </row>
     <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="19" t="inlineStr">
+      <c r="A65" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4805,28 +6628,42 @@
       <c r="D65" s="3" t="inlineStr"/>
       <c r="E65" s="3" t="inlineStr"/>
       <c r="F65" s="3" t="inlineStr"/>
-      <c r="G65" s="20" t="n">
-        <v>92000</v>
-      </c>
-      <c r="H65" s="20" t="n">
-        <v>184000</v>
-      </c>
-      <c r="I65" s="20" t="n">
-        <v>207000</v>
-      </c>
+      <c r="G65" s="3" t="inlineStr"/>
+      <c r="H65" s="3" t="inlineStr"/>
+      <c r="I65" s="3" t="inlineStr"/>
       <c r="J65" s="3" t="inlineStr"/>
-      <c r="K65" s="3" t="inlineStr"/>
-      <c r="L65" s="3" t="inlineStr"/>
+      <c r="K65" s="22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="L65" s="22" t="n">
+        <v>153009</v>
+      </c>
       <c r="M65" s="3" t="inlineStr"/>
       <c r="N65" s="3" t="inlineStr"/>
-      <c r="O65" s="3" t="inlineStr"/>
-      <c r="P65" s="3" t="inlineStr"/>
-      <c r="Q65" s="3" t="inlineStr"/>
-      <c r="R65" s="3" t="inlineStr"/>
-      <c r="S65" s="3" t="inlineStr"/>
-      <c r="T65" s="3" t="inlineStr"/>
-      <c r="U65" s="3" t="inlineStr"/>
-      <c r="V65" s="3" t="inlineStr"/>
+      <c r="O65" s="22" t="n">
+        <v>92000</v>
+      </c>
+      <c r="P65" s="22" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q65" s="22" t="n">
+        <v>207000</v>
+      </c>
+      <c r="R65" s="22" t="n">
+        <v>218500</v>
+      </c>
+      <c r="S65" s="22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="T65" s="22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U65" s="22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="V65" s="22" t="n">
+        <v>230000</v>
+      </c>
       <c r="W65" s="3" t="inlineStr"/>
       <c r="X65" s="3" t="inlineStr"/>
       <c r="Y65" s="3" t="inlineStr"/>
@@ -4839,7 +6676,7 @@
       <c r="AF65" s="3" t="inlineStr"/>
     </row>
     <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="19" t="inlineStr">
+      <c r="A66" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -4849,28 +6686,42 @@
       <c r="D66" s="3" t="inlineStr"/>
       <c r="E66" s="3" t="inlineStr"/>
       <c r="F66" s="3" t="inlineStr"/>
-      <c r="G66" s="20" t="n">
-        <v>92000</v>
-      </c>
-      <c r="H66" s="20" t="n">
-        <v>184000</v>
-      </c>
-      <c r="I66" s="20" t="n">
-        <v>207000</v>
-      </c>
+      <c r="G66" s="3" t="inlineStr"/>
+      <c r="H66" s="3" t="inlineStr"/>
+      <c r="I66" s="3" t="inlineStr"/>
       <c r="J66" s="3" t="inlineStr"/>
-      <c r="K66" s="3" t="inlineStr"/>
-      <c r="L66" s="3" t="inlineStr"/>
+      <c r="K66" s="22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="L66" s="22" t="n">
+        <v>153009</v>
+      </c>
       <c r="M66" s="3" t="inlineStr"/>
       <c r="N66" s="3" t="inlineStr"/>
-      <c r="O66" s="3" t="inlineStr"/>
-      <c r="P66" s="3" t="inlineStr"/>
-      <c r="Q66" s="3" t="inlineStr"/>
-      <c r="R66" s="3" t="inlineStr"/>
-      <c r="S66" s="3" t="inlineStr"/>
-      <c r="T66" s="3" t="inlineStr"/>
-      <c r="U66" s="3" t="inlineStr"/>
-      <c r="V66" s="3" t="inlineStr"/>
+      <c r="O66" s="22" t="n">
+        <v>92000</v>
+      </c>
+      <c r="P66" s="22" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q66" s="22" t="n">
+        <v>207000</v>
+      </c>
+      <c r="R66" s="22" t="n">
+        <v>218500</v>
+      </c>
+      <c r="S66" s="22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="T66" s="22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U66" s="22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="V66" s="22" t="n">
+        <v>230000</v>
+      </c>
       <c r="W66" s="3" t="inlineStr"/>
       <c r="X66" s="3" t="inlineStr"/>
       <c r="Y66" s="3" t="inlineStr"/>
@@ -4917,31 +6768,19 @@
       <c r="AF67" s="3" t="inlineStr"/>
     </row>
     <row r="68" ht="22" customHeight="1">
-      <c r="A68" s="21" t="inlineStr">
+      <c r="A68" s="23" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B68" s="22" t="n">
-        <v>230000</v>
-      </c>
-      <c r="C68" s="22" t="n">
-        <v>230000</v>
-      </c>
-      <c r="D68" s="22" t="n">
-        <v>180082</v>
-      </c>
+      <c r="B68" s="3" t="inlineStr"/>
+      <c r="C68" s="3" t="inlineStr"/>
+      <c r="D68" s="3" t="inlineStr"/>
       <c r="E68" s="3" t="inlineStr"/>
       <c r="F68" s="3" t="inlineStr"/>
-      <c r="G68" s="22" t="n">
-        <v>92000</v>
-      </c>
-      <c r="H68" s="22" t="n">
-        <v>184000</v>
-      </c>
-      <c r="I68" s="22" t="n">
-        <v>207000</v>
-      </c>
+      <c r="G68" s="3" t="inlineStr"/>
+      <c r="H68" s="3" t="inlineStr"/>
+      <c r="I68" s="3" t="inlineStr"/>
       <c r="J68" s="3" t="inlineStr"/>
       <c r="K68" s="3" t="inlineStr"/>
       <c r="L68" s="3" t="inlineStr"/>
@@ -4952,11 +6791,21 @@
       <c r="Q68" s="3" t="inlineStr"/>
       <c r="R68" s="3" t="inlineStr"/>
       <c r="S68" s="3" t="inlineStr"/>
-      <c r="T68" s="3" t="inlineStr"/>
-      <c r="U68" s="3" t="inlineStr"/>
-      <c r="V68" s="3" t="inlineStr"/>
-      <c r="W68" s="3" t="inlineStr"/>
-      <c r="X68" s="3" t="inlineStr"/>
+      <c r="T68" s="24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U68" s="24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="V68" s="24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="W68" s="24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="X68" s="24" t="n">
+        <v>230000</v>
+      </c>
       <c r="Y68" s="3" t="inlineStr"/>
       <c r="Z68" s="3" t="inlineStr"/>
       <c r="AA68" s="3" t="inlineStr"/>
@@ -4967,31 +6816,19 @@
       <c r="AF68" s="3" t="inlineStr"/>
     </row>
     <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="21" t="inlineStr">
+      <c r="A69" s="23" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B69" s="22" t="n">
-        <v>230000</v>
-      </c>
-      <c r="C69" s="22" t="n">
-        <v>230000</v>
-      </c>
-      <c r="D69" s="22" t="n">
-        <v>180082</v>
-      </c>
+      <c r="B69" s="3" t="inlineStr"/>
+      <c r="C69" s="3" t="inlineStr"/>
+      <c r="D69" s="3" t="inlineStr"/>
       <c r="E69" s="3" t="inlineStr"/>
       <c r="F69" s="3" t="inlineStr"/>
-      <c r="G69" s="22" t="n">
-        <v>92000</v>
-      </c>
-      <c r="H69" s="22" t="n">
-        <v>184000</v>
-      </c>
-      <c r="I69" s="22" t="n">
-        <v>207000</v>
-      </c>
+      <c r="G69" s="3" t="inlineStr"/>
+      <c r="H69" s="3" t="inlineStr"/>
+      <c r="I69" s="3" t="inlineStr"/>
       <c r="J69" s="3" t="inlineStr"/>
       <c r="K69" s="3" t="inlineStr"/>
       <c r="L69" s="3" t="inlineStr"/>
@@ -4999,14 +6836,30 @@
       <c r="N69" s="3" t="inlineStr"/>
       <c r="O69" s="3" t="inlineStr"/>
       <c r="P69" s="3" t="inlineStr"/>
-      <c r="Q69" s="3" t="inlineStr"/>
-      <c r="R69" s="3" t="inlineStr"/>
-      <c r="S69" s="3" t="inlineStr"/>
-      <c r="T69" s="3" t="inlineStr"/>
-      <c r="U69" s="3" t="inlineStr"/>
-      <c r="V69" s="3" t="inlineStr"/>
-      <c r="W69" s="3" t="inlineStr"/>
-      <c r="X69" s="3" t="inlineStr"/>
+      <c r="Q69" s="24" t="n">
+        <v>207000</v>
+      </c>
+      <c r="R69" s="24" t="n">
+        <v>218500</v>
+      </c>
+      <c r="S69" s="24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="T69" s="24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U69" s="24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="V69" s="24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="W69" s="24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="X69" s="24" t="n">
+        <v>230000</v>
+      </c>
       <c r="Y69" s="3" t="inlineStr"/>
       <c r="Z69" s="3" t="inlineStr"/>
       <c r="AA69" s="3" t="inlineStr"/>
@@ -5017,46 +6870,54 @@
       <c r="AF69" s="3" t="inlineStr"/>
     </row>
     <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="21" t="inlineStr">
+      <c r="A70" s="23" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B70" s="22" t="n">
-        <v>230000</v>
-      </c>
-      <c r="C70" s="22" t="n">
-        <v>230000</v>
-      </c>
-      <c r="D70" s="22" t="n">
-        <v>180082</v>
-      </c>
+      <c r="B70" s="3" t="inlineStr"/>
+      <c r="C70" s="3" t="inlineStr"/>
+      <c r="D70" s="3" t="inlineStr"/>
       <c r="E70" s="3" t="inlineStr"/>
       <c r="F70" s="3" t="inlineStr"/>
-      <c r="G70" s="22" t="n">
-        <v>92000</v>
-      </c>
-      <c r="H70" s="22" t="n">
-        <v>184000</v>
-      </c>
-      <c r="I70" s="22" t="n">
-        <v>207000</v>
-      </c>
+      <c r="G70" s="3" t="inlineStr"/>
+      <c r="H70" s="3" t="inlineStr"/>
+      <c r="I70" s="3" t="inlineStr"/>
       <c r="J70" s="3" t="inlineStr"/>
       <c r="K70" s="3" t="inlineStr"/>
       <c r="L70" s="3" t="inlineStr"/>
       <c r="M70" s="3" t="inlineStr"/>
       <c r="N70" s="3" t="inlineStr"/>
-      <c r="O70" s="3" t="inlineStr"/>
-      <c r="P70" s="3" t="inlineStr"/>
-      <c r="Q70" s="3" t="inlineStr"/>
-      <c r="R70" s="3" t="inlineStr"/>
-      <c r="S70" s="3" t="inlineStr"/>
-      <c r="T70" s="3" t="inlineStr"/>
-      <c r="U70" s="3" t="inlineStr"/>
-      <c r="V70" s="3" t="inlineStr"/>
-      <c r="W70" s="3" t="inlineStr"/>
-      <c r="X70" s="3" t="inlineStr"/>
+      <c r="O70" s="24" t="n">
+        <v>92000</v>
+      </c>
+      <c r="P70" s="24" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q70" s="24" t="n">
+        <v>207000</v>
+      </c>
+      <c r="R70" s="24" t="n">
+        <v>218500</v>
+      </c>
+      <c r="S70" s="24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="T70" s="24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U70" s="24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="V70" s="24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="W70" s="24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="X70" s="24" t="n">
+        <v>230000</v>
+      </c>
       <c r="Y70" s="3" t="inlineStr"/>
       <c r="Z70" s="3" t="inlineStr"/>
       <c r="AA70" s="3" t="inlineStr"/>
@@ -5067,20 +6928,14 @@
       <c r="AF70" s="3" t="inlineStr"/>
     </row>
     <row r="71" ht="22" customHeight="1">
-      <c r="A71" s="21" t="inlineStr">
+      <c r="A71" s="23" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B71" s="22" t="n">
-        <v>230000</v>
-      </c>
-      <c r="C71" s="22" t="n">
-        <v>230000</v>
-      </c>
-      <c r="D71" s="22" t="n">
-        <v>180082</v>
-      </c>
+      <c r="B71" s="3" t="inlineStr"/>
+      <c r="C71" s="3" t="inlineStr"/>
+      <c r="D71" s="3" t="inlineStr"/>
       <c r="E71" s="3" t="inlineStr"/>
       <c r="F71" s="3" t="inlineStr"/>
       <c r="G71" s="3" t="inlineStr"/>
@@ -5091,16 +6946,36 @@
       <c r="L71" s="3" t="inlineStr"/>
       <c r="M71" s="3" t="inlineStr"/>
       <c r="N71" s="3" t="inlineStr"/>
-      <c r="O71" s="3" t="inlineStr"/>
-      <c r="P71" s="3" t="inlineStr"/>
-      <c r="Q71" s="3" t="inlineStr"/>
-      <c r="R71" s="3" t="inlineStr"/>
-      <c r="S71" s="3" t="inlineStr"/>
-      <c r="T71" s="3" t="inlineStr"/>
-      <c r="U71" s="3" t="inlineStr"/>
-      <c r="V71" s="3" t="inlineStr"/>
-      <c r="W71" s="3" t="inlineStr"/>
-      <c r="X71" s="3" t="inlineStr"/>
+      <c r="O71" s="24" t="n">
+        <v>92000</v>
+      </c>
+      <c r="P71" s="24" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q71" s="24" t="n">
+        <v>207000</v>
+      </c>
+      <c r="R71" s="24" t="n">
+        <v>218500</v>
+      </c>
+      <c r="S71" s="24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="T71" s="24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U71" s="24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="V71" s="24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="W71" s="24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="X71" s="24" t="n">
+        <v>230000</v>
+      </c>
       <c r="Y71" s="3" t="inlineStr"/>
       <c r="Z71" s="3" t="inlineStr"/>
       <c r="AA71" s="3" t="inlineStr"/>
@@ -5111,20 +6986,14 @@
       <c r="AF71" s="3" t="inlineStr"/>
     </row>
     <row r="72" ht="22" customHeight="1">
-      <c r="A72" s="21" t="inlineStr">
+      <c r="A72" s="23" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B72" s="22" t="n">
-        <v>230000</v>
-      </c>
-      <c r="C72" s="22" t="n">
-        <v>230000</v>
-      </c>
-      <c r="D72" s="22" t="n">
-        <v>180082</v>
-      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="3" t="inlineStr"/>
+      <c r="D72" s="3" t="inlineStr"/>
       <c r="E72" s="3" t="inlineStr"/>
       <c r="F72" s="3" t="inlineStr"/>
       <c r="G72" s="3" t="inlineStr"/>
@@ -5135,16 +7004,36 @@
       <c r="L72" s="3" t="inlineStr"/>
       <c r="M72" s="3" t="inlineStr"/>
       <c r="N72" s="3" t="inlineStr"/>
-      <c r="O72" s="3" t="inlineStr"/>
-      <c r="P72" s="3" t="inlineStr"/>
-      <c r="Q72" s="3" t="inlineStr"/>
-      <c r="R72" s="3" t="inlineStr"/>
-      <c r="S72" s="3" t="inlineStr"/>
-      <c r="T72" s="3" t="inlineStr"/>
-      <c r="U72" s="3" t="inlineStr"/>
-      <c r="V72" s="3" t="inlineStr"/>
-      <c r="W72" s="3" t="inlineStr"/>
-      <c r="X72" s="3" t="inlineStr"/>
+      <c r="O72" s="24" t="n">
+        <v>92000</v>
+      </c>
+      <c r="P72" s="24" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q72" s="24" t="n">
+        <v>207000</v>
+      </c>
+      <c r="R72" s="24" t="n">
+        <v>218500</v>
+      </c>
+      <c r="S72" s="24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="T72" s="24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U72" s="24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="V72" s="24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="W72" s="24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="X72" s="24" t="n">
+        <v>230000</v>
+      </c>
       <c r="Y72" s="3" t="inlineStr"/>
       <c r="Z72" s="3" t="inlineStr"/>
       <c r="AA72" s="3" t="inlineStr"/>
@@ -5155,7 +7044,11 @@
       <c r="AF72" s="3" t="inlineStr"/>
     </row>
     <row r="73" ht="22" customHeight="1">
-      <c r="A73" s="6" t="inlineStr"/>
+      <c r="A73" s="23" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
       <c r="B73" s="3" t="inlineStr"/>
       <c r="C73" s="3" t="inlineStr"/>
       <c r="D73" s="3" t="inlineStr"/>
@@ -5177,8 +7070,12 @@
       <c r="T73" s="3" t="inlineStr"/>
       <c r="U73" s="3" t="inlineStr"/>
       <c r="V73" s="3" t="inlineStr"/>
-      <c r="W73" s="3" t="inlineStr"/>
-      <c r="X73" s="3" t="inlineStr"/>
+      <c r="W73" s="24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="X73" s="24" t="n">
+        <v>230000</v>
+      </c>
       <c r="Y73" s="3" t="inlineStr"/>
       <c r="Z73" s="3" t="inlineStr"/>
       <c r="AA73" s="3" t="inlineStr"/>
@@ -5189,112 +7086,1134 @@
       <c r="AF73" s="3" t="inlineStr"/>
     </row>
     <row r="74" ht="22" customHeight="1">
-      <c r="A74" s="23" t="inlineStr">
+      <c r="A74" s="6" t="inlineStr"/>
+      <c r="B74" s="3" t="inlineStr"/>
+      <c r="C74" s="3" t="inlineStr"/>
+      <c r="D74" s="3" t="inlineStr"/>
+      <c r="E74" s="3" t="inlineStr"/>
+      <c r="F74" s="3" t="inlineStr"/>
+      <c r="G74" s="3" t="inlineStr"/>
+      <c r="H74" s="3" t="inlineStr"/>
+      <c r="I74" s="3" t="inlineStr"/>
+      <c r="J74" s="3" t="inlineStr"/>
+      <c r="K74" s="3" t="inlineStr"/>
+      <c r="L74" s="3" t="inlineStr"/>
+      <c r="M74" s="3" t="inlineStr"/>
+      <c r="N74" s="3" t="inlineStr"/>
+      <c r="O74" s="3" t="inlineStr"/>
+      <c r="P74" s="3" t="inlineStr"/>
+      <c r="Q74" s="3" t="inlineStr"/>
+      <c r="R74" s="3" t="inlineStr"/>
+      <c r="S74" s="3" t="inlineStr"/>
+      <c r="T74" s="3" t="inlineStr"/>
+      <c r="U74" s="3" t="inlineStr"/>
+      <c r="V74" s="3" t="inlineStr"/>
+      <c r="W74" s="3" t="inlineStr"/>
+      <c r="X74" s="3" t="inlineStr"/>
+      <c r="Y74" s="3" t="inlineStr"/>
+      <c r="Z74" s="3" t="inlineStr"/>
+      <c r="AA74" s="3" t="inlineStr"/>
+      <c r="AB74" s="3" t="inlineStr"/>
+      <c r="AC74" s="3" t="inlineStr"/>
+      <c r="AD74" s="3" t="inlineStr"/>
+      <c r="AE74" s="3" t="inlineStr"/>
+      <c r="AF74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="25" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr"/>
+      <c r="C75" s="3" t="inlineStr"/>
+      <c r="D75" s="3" t="inlineStr"/>
+      <c r="E75" s="3" t="inlineStr"/>
+      <c r="F75" s="3" t="inlineStr"/>
+      <c r="G75" s="3" t="inlineStr"/>
+      <c r="H75" s="3" t="inlineStr"/>
+      <c r="I75" s="3" t="inlineStr"/>
+      <c r="J75" s="3" t="inlineStr"/>
+      <c r="K75" s="3" t="inlineStr"/>
+      <c r="L75" s="3" t="inlineStr"/>
+      <c r="M75" s="3" t="inlineStr"/>
+      <c r="N75" s="3" t="inlineStr"/>
+      <c r="O75" s="3" t="inlineStr"/>
+      <c r="P75" s="3" t="inlineStr"/>
+      <c r="Q75" s="3" t="inlineStr"/>
+      <c r="R75" s="3" t="inlineStr"/>
+      <c r="S75" s="3" t="inlineStr"/>
+      <c r="T75" s="3" t="inlineStr"/>
+      <c r="U75" s="3" t="inlineStr"/>
+      <c r="V75" s="3" t="inlineStr"/>
+      <c r="W75" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="X75" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Y75" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z75" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA75" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB75" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AC75" s="3" t="inlineStr"/>
+      <c r="AD75" s="3" t="inlineStr"/>
+      <c r="AE75" s="3" t="inlineStr"/>
+      <c r="AF75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="25" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr"/>
+      <c r="C76" s="3" t="inlineStr"/>
+      <c r="D76" s="3" t="inlineStr"/>
+      <c r="E76" s="3" t="inlineStr"/>
+      <c r="F76" s="3" t="inlineStr"/>
+      <c r="G76" s="3" t="inlineStr"/>
+      <c r="H76" s="3" t="inlineStr"/>
+      <c r="I76" s="3" t="inlineStr"/>
+      <c r="J76" s="3" t="inlineStr"/>
+      <c r="K76" s="3" t="inlineStr"/>
+      <c r="L76" s="3" t="inlineStr"/>
+      <c r="M76" s="3" t="inlineStr"/>
+      <c r="N76" s="3" t="inlineStr"/>
+      <c r="O76" s="3" t="inlineStr"/>
+      <c r="P76" s="3" t="inlineStr"/>
+      <c r="Q76" s="3" t="inlineStr"/>
+      <c r="R76" s="3" t="inlineStr"/>
+      <c r="S76" s="3" t="inlineStr"/>
+      <c r="T76" s="3" t="inlineStr"/>
+      <c r="U76" s="3" t="inlineStr"/>
+      <c r="V76" s="3" t="inlineStr"/>
+      <c r="W76" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="X76" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Y76" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z76" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA76" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB76" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AC76" s="3" t="inlineStr"/>
+      <c r="AD76" s="3" t="inlineStr"/>
+      <c r="AE76" s="3" t="inlineStr"/>
+      <c r="AF76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="25" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr"/>
+      <c r="C77" s="3" t="inlineStr"/>
+      <c r="D77" s="3" t="inlineStr"/>
+      <c r="E77" s="3" t="inlineStr"/>
+      <c r="F77" s="3" t="inlineStr"/>
+      <c r="G77" s="3" t="inlineStr"/>
+      <c r="H77" s="3" t="inlineStr"/>
+      <c r="I77" s="3" t="inlineStr"/>
+      <c r="J77" s="3" t="inlineStr"/>
+      <c r="K77" s="3" t="inlineStr"/>
+      <c r="L77" s="3" t="inlineStr"/>
+      <c r="M77" s="3" t="inlineStr"/>
+      <c r="N77" s="3" t="inlineStr"/>
+      <c r="O77" s="3" t="inlineStr"/>
+      <c r="P77" s="3" t="inlineStr"/>
+      <c r="Q77" s="3" t="inlineStr"/>
+      <c r="R77" s="3" t="inlineStr"/>
+      <c r="S77" s="3" t="inlineStr"/>
+      <c r="T77" s="3" t="inlineStr"/>
+      <c r="U77" s="3" t="inlineStr"/>
+      <c r="V77" s="3" t="inlineStr"/>
+      <c r="W77" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="X77" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Y77" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z77" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA77" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB77" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AC77" s="3" t="inlineStr"/>
+      <c r="AD77" s="3" t="inlineStr"/>
+      <c r="AE77" s="3" t="inlineStr"/>
+      <c r="AF77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="25" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr"/>
+      <c r="C78" s="3" t="inlineStr"/>
+      <c r="D78" s="3" t="inlineStr"/>
+      <c r="E78" s="3" t="inlineStr"/>
+      <c r="F78" s="3" t="inlineStr"/>
+      <c r="G78" s="3" t="inlineStr"/>
+      <c r="H78" s="3" t="inlineStr"/>
+      <c r="I78" s="3" t="inlineStr"/>
+      <c r="J78" s="3" t="inlineStr"/>
+      <c r="K78" s="3" t="inlineStr"/>
+      <c r="L78" s="3" t="inlineStr"/>
+      <c r="M78" s="3" t="inlineStr"/>
+      <c r="N78" s="3" t="inlineStr"/>
+      <c r="O78" s="3" t="inlineStr"/>
+      <c r="P78" s="3" t="inlineStr"/>
+      <c r="Q78" s="3" t="inlineStr"/>
+      <c r="R78" s="3" t="inlineStr"/>
+      <c r="S78" s="3" t="inlineStr"/>
+      <c r="T78" s="3" t="inlineStr"/>
+      <c r="U78" s="3" t="inlineStr"/>
+      <c r="V78" s="3" t="inlineStr"/>
+      <c r="W78" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="X78" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Y78" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z78" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA78" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB78" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AC78" s="3" t="inlineStr"/>
+      <c r="AD78" s="3" t="inlineStr"/>
+      <c r="AE78" s="3" t="inlineStr"/>
+      <c r="AF78" s="3" t="inlineStr"/>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="25" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr"/>
+      <c r="C79" s="3" t="inlineStr"/>
+      <c r="D79" s="3" t="inlineStr"/>
+      <c r="E79" s="3" t="inlineStr"/>
+      <c r="F79" s="3" t="inlineStr"/>
+      <c r="G79" s="3" t="inlineStr"/>
+      <c r="H79" s="3" t="inlineStr"/>
+      <c r="I79" s="3" t="inlineStr"/>
+      <c r="J79" s="3" t="inlineStr"/>
+      <c r="K79" s="3" t="inlineStr"/>
+      <c r="L79" s="3" t="inlineStr"/>
+      <c r="M79" s="3" t="inlineStr"/>
+      <c r="N79" s="3" t="inlineStr"/>
+      <c r="O79" s="3" t="inlineStr"/>
+      <c r="P79" s="3" t="inlineStr"/>
+      <c r="Q79" s="3" t="inlineStr"/>
+      <c r="R79" s="3" t="inlineStr"/>
+      <c r="S79" s="3" t="inlineStr"/>
+      <c r="T79" s="3" t="inlineStr"/>
+      <c r="U79" s="3" t="inlineStr"/>
+      <c r="V79" s="3" t="inlineStr"/>
+      <c r="W79" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="X79" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Y79" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z79" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA79" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB79" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AC79" s="3" t="inlineStr"/>
+      <c r="AD79" s="3" t="inlineStr"/>
+      <c r="AE79" s="3" t="inlineStr"/>
+      <c r="AF79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="25" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr"/>
+      <c r="C80" s="3" t="inlineStr"/>
+      <c r="D80" s="3" t="inlineStr"/>
+      <c r="E80" s="3" t="inlineStr"/>
+      <c r="F80" s="3" t="inlineStr"/>
+      <c r="G80" s="3" t="inlineStr"/>
+      <c r="H80" s="3" t="inlineStr"/>
+      <c r="I80" s="3" t="inlineStr"/>
+      <c r="J80" s="3" t="inlineStr"/>
+      <c r="K80" s="3" t="inlineStr"/>
+      <c r="L80" s="3" t="inlineStr"/>
+      <c r="M80" s="3" t="inlineStr"/>
+      <c r="N80" s="3" t="inlineStr"/>
+      <c r="O80" s="3" t="inlineStr"/>
+      <c r="P80" s="3" t="inlineStr"/>
+      <c r="Q80" s="3" t="inlineStr"/>
+      <c r="R80" s="3" t="inlineStr"/>
+      <c r="S80" s="3" t="inlineStr"/>
+      <c r="T80" s="3" t="inlineStr"/>
+      <c r="U80" s="3" t="inlineStr"/>
+      <c r="V80" s="3" t="inlineStr"/>
+      <c r="W80" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="X80" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Y80" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z80" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA80" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB80" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AC80" s="3" t="inlineStr"/>
+      <c r="AD80" s="3" t="inlineStr"/>
+      <c r="AE80" s="3" t="inlineStr"/>
+      <c r="AF80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="6" t="inlineStr"/>
+      <c r="B81" s="3" t="inlineStr"/>
+      <c r="C81" s="3" t="inlineStr"/>
+      <c r="D81" s="3" t="inlineStr"/>
+      <c r="E81" s="3" t="inlineStr"/>
+      <c r="F81" s="3" t="inlineStr"/>
+      <c r="G81" s="3" t="inlineStr"/>
+      <c r="H81" s="3" t="inlineStr"/>
+      <c r="I81" s="3" t="inlineStr"/>
+      <c r="J81" s="3" t="inlineStr"/>
+      <c r="K81" s="3" t="inlineStr"/>
+      <c r="L81" s="3" t="inlineStr"/>
+      <c r="M81" s="3" t="inlineStr"/>
+      <c r="N81" s="3" t="inlineStr"/>
+      <c r="O81" s="3" t="inlineStr"/>
+      <c r="P81" s="3" t="inlineStr"/>
+      <c r="Q81" s="3" t="inlineStr"/>
+      <c r="R81" s="3" t="inlineStr"/>
+      <c r="S81" s="3" t="inlineStr"/>
+      <c r="T81" s="3" t="inlineStr"/>
+      <c r="U81" s="3" t="inlineStr"/>
+      <c r="V81" s="3" t="inlineStr"/>
+      <c r="W81" s="3" t="inlineStr"/>
+      <c r="X81" s="3" t="inlineStr"/>
+      <c r="Y81" s="3" t="inlineStr"/>
+      <c r="Z81" s="3" t="inlineStr"/>
+      <c r="AA81" s="3" t="inlineStr"/>
+      <c r="AB81" s="3" t="inlineStr"/>
+      <c r="AC81" s="3" t="inlineStr"/>
+      <c r="AD81" s="3" t="inlineStr"/>
+      <c r="AE81" s="3" t="inlineStr"/>
+      <c r="AF81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="27" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr"/>
+      <c r="C82" s="3" t="inlineStr"/>
+      <c r="D82" s="3" t="inlineStr"/>
+      <c r="E82" s="3" t="inlineStr"/>
+      <c r="F82" s="3" t="inlineStr"/>
+      <c r="G82" s="3" t="inlineStr"/>
+      <c r="H82" s="3" t="inlineStr"/>
+      <c r="I82" s="3" t="inlineStr"/>
+      <c r="J82" s="3" t="inlineStr"/>
+      <c r="K82" s="3" t="inlineStr"/>
+      <c r="L82" s="3" t="inlineStr"/>
+      <c r="M82" s="3" t="inlineStr"/>
+      <c r="N82" s="3" t="inlineStr"/>
+      <c r="O82" s="3" t="inlineStr"/>
+      <c r="P82" s="3" t="inlineStr"/>
+      <c r="Q82" s="3" t="inlineStr"/>
+      <c r="R82" s="3" t="inlineStr"/>
+      <c r="S82" s="3" t="inlineStr"/>
+      <c r="T82" s="3" t="inlineStr"/>
+      <c r="U82" s="3" t="inlineStr"/>
+      <c r="V82" s="3" t="inlineStr"/>
+      <c r="W82" s="3" t="inlineStr"/>
+      <c r="X82" s="3" t="inlineStr"/>
+      <c r="Y82" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z82" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA82" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB82" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AC82" s="3" t="inlineStr"/>
+      <c r="AD82" s="3" t="inlineStr"/>
+      <c r="AE82" s="3" t="inlineStr"/>
+      <c r="AF82" s="3" t="inlineStr"/>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="27" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr"/>
+      <c r="C83" s="3" t="inlineStr"/>
+      <c r="D83" s="3" t="inlineStr"/>
+      <c r="E83" s="3" t="inlineStr"/>
+      <c r="F83" s="3" t="inlineStr"/>
+      <c r="G83" s="3" t="inlineStr"/>
+      <c r="H83" s="3" t="inlineStr"/>
+      <c r="I83" s="3" t="inlineStr"/>
+      <c r="J83" s="3" t="inlineStr"/>
+      <c r="K83" s="3" t="inlineStr"/>
+      <c r="L83" s="3" t="inlineStr"/>
+      <c r="M83" s="3" t="inlineStr"/>
+      <c r="N83" s="3" t="inlineStr"/>
+      <c r="O83" s="3" t="inlineStr"/>
+      <c r="P83" s="3" t="inlineStr"/>
+      <c r="Q83" s="3" t="inlineStr"/>
+      <c r="R83" s="3" t="inlineStr"/>
+      <c r="S83" s="3" t="inlineStr"/>
+      <c r="T83" s="3" t="inlineStr"/>
+      <c r="U83" s="3" t="inlineStr"/>
+      <c r="V83" s="3" t="inlineStr"/>
+      <c r="W83" s="3" t="inlineStr"/>
+      <c r="X83" s="3" t="inlineStr"/>
+      <c r="Y83" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z83" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA83" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB83" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AC83" s="3" t="inlineStr"/>
+      <c r="AD83" s="3" t="inlineStr"/>
+      <c r="AE83" s="3" t="inlineStr"/>
+      <c r="AF83" s="3" t="inlineStr"/>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="27" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr"/>
+      <c r="C84" s="3" t="inlineStr"/>
+      <c r="D84" s="3" t="inlineStr"/>
+      <c r="E84" s="3" t="inlineStr"/>
+      <c r="F84" s="3" t="inlineStr"/>
+      <c r="G84" s="3" t="inlineStr"/>
+      <c r="H84" s="3" t="inlineStr"/>
+      <c r="I84" s="3" t="inlineStr"/>
+      <c r="J84" s="3" t="inlineStr"/>
+      <c r="K84" s="3" t="inlineStr"/>
+      <c r="L84" s="3" t="inlineStr"/>
+      <c r="M84" s="3" t="inlineStr"/>
+      <c r="N84" s="3" t="inlineStr"/>
+      <c r="O84" s="3" t="inlineStr"/>
+      <c r="P84" s="3" t="inlineStr"/>
+      <c r="Q84" s="3" t="inlineStr"/>
+      <c r="R84" s="3" t="inlineStr"/>
+      <c r="S84" s="3" t="inlineStr"/>
+      <c r="T84" s="3" t="inlineStr"/>
+      <c r="U84" s="3" t="inlineStr"/>
+      <c r="V84" s="3" t="inlineStr"/>
+      <c r="W84" s="3" t="inlineStr"/>
+      <c r="X84" s="3" t="inlineStr"/>
+      <c r="Y84" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z84" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA84" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB84" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AC84" s="3" t="inlineStr"/>
+      <c r="AD84" s="3" t="inlineStr"/>
+      <c r="AE84" s="3" t="inlineStr"/>
+      <c r="AF84" s="3" t="inlineStr"/>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="27" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr"/>
+      <c r="C85" s="3" t="inlineStr"/>
+      <c r="D85" s="3" t="inlineStr"/>
+      <c r="E85" s="3" t="inlineStr"/>
+      <c r="F85" s="3" t="inlineStr"/>
+      <c r="G85" s="3" t="inlineStr"/>
+      <c r="H85" s="3" t="inlineStr"/>
+      <c r="I85" s="3" t="inlineStr"/>
+      <c r="J85" s="3" t="inlineStr"/>
+      <c r="K85" s="3" t="inlineStr"/>
+      <c r="L85" s="3" t="inlineStr"/>
+      <c r="M85" s="3" t="inlineStr"/>
+      <c r="N85" s="3" t="inlineStr"/>
+      <c r="O85" s="3" t="inlineStr"/>
+      <c r="P85" s="3" t="inlineStr"/>
+      <c r="Q85" s="3" t="inlineStr"/>
+      <c r="R85" s="3" t="inlineStr"/>
+      <c r="S85" s="3" t="inlineStr"/>
+      <c r="T85" s="3" t="inlineStr"/>
+      <c r="U85" s="3" t="inlineStr"/>
+      <c r="V85" s="3" t="inlineStr"/>
+      <c r="W85" s="3" t="inlineStr"/>
+      <c r="X85" s="3" t="inlineStr"/>
+      <c r="Y85" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z85" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA85" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB85" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AC85" s="3" t="inlineStr"/>
+      <c r="AD85" s="3" t="inlineStr"/>
+      <c r="AE85" s="3" t="inlineStr"/>
+      <c r="AF85" s="3" t="inlineStr"/>
+    </row>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="27" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr"/>
+      <c r="C86" s="3" t="inlineStr"/>
+      <c r="D86" s="3" t="inlineStr"/>
+      <c r="E86" s="3" t="inlineStr"/>
+      <c r="F86" s="3" t="inlineStr"/>
+      <c r="G86" s="3" t="inlineStr"/>
+      <c r="H86" s="3" t="inlineStr"/>
+      <c r="I86" s="3" t="inlineStr"/>
+      <c r="J86" s="3" t="inlineStr"/>
+      <c r="K86" s="3" t="inlineStr"/>
+      <c r="L86" s="3" t="inlineStr"/>
+      <c r="M86" s="3" t="inlineStr"/>
+      <c r="N86" s="3" t="inlineStr"/>
+      <c r="O86" s="3" t="inlineStr"/>
+      <c r="P86" s="3" t="inlineStr"/>
+      <c r="Q86" s="3" t="inlineStr"/>
+      <c r="R86" s="3" t="inlineStr"/>
+      <c r="S86" s="3" t="inlineStr"/>
+      <c r="T86" s="3" t="inlineStr"/>
+      <c r="U86" s="3" t="inlineStr"/>
+      <c r="V86" s="3" t="inlineStr"/>
+      <c r="W86" s="3" t="inlineStr"/>
+      <c r="X86" s="3" t="inlineStr"/>
+      <c r="Y86" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z86" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA86" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB86" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AC86" s="3" t="inlineStr"/>
+      <c r="AD86" s="3" t="inlineStr"/>
+      <c r="AE86" s="3" t="inlineStr"/>
+      <c r="AF86" s="3" t="inlineStr"/>
+    </row>
+    <row r="87" ht="22" customHeight="1">
+      <c r="A87" s="27" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr"/>
+      <c r="C87" s="3" t="inlineStr"/>
+      <c r="D87" s="3" t="inlineStr"/>
+      <c r="E87" s="3" t="inlineStr"/>
+      <c r="F87" s="3" t="inlineStr"/>
+      <c r="G87" s="3" t="inlineStr"/>
+      <c r="H87" s="3" t="inlineStr"/>
+      <c r="I87" s="3" t="inlineStr"/>
+      <c r="J87" s="3" t="inlineStr"/>
+      <c r="K87" s="3" t="inlineStr"/>
+      <c r="L87" s="3" t="inlineStr"/>
+      <c r="M87" s="3" t="inlineStr"/>
+      <c r="N87" s="3" t="inlineStr"/>
+      <c r="O87" s="3" t="inlineStr"/>
+      <c r="P87" s="3" t="inlineStr"/>
+      <c r="Q87" s="3" t="inlineStr"/>
+      <c r="R87" s="3" t="inlineStr"/>
+      <c r="S87" s="3" t="inlineStr"/>
+      <c r="T87" s="3" t="inlineStr"/>
+      <c r="U87" s="3" t="inlineStr"/>
+      <c r="V87" s="3" t="inlineStr"/>
+      <c r="W87" s="3" t="inlineStr"/>
+      <c r="X87" s="3" t="inlineStr"/>
+      <c r="Y87" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z87" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA87" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB87" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AC87" s="3" t="inlineStr"/>
+      <c r="AD87" s="3" t="inlineStr"/>
+      <c r="AE87" s="3" t="inlineStr"/>
+      <c r="AF87" s="3" t="inlineStr"/>
+    </row>
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="27" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr"/>
+      <c r="C88" s="3" t="inlineStr"/>
+      <c r="D88" s="3" t="inlineStr"/>
+      <c r="E88" s="3" t="inlineStr"/>
+      <c r="F88" s="3" t="inlineStr"/>
+      <c r="G88" s="3" t="inlineStr"/>
+      <c r="H88" s="3" t="inlineStr"/>
+      <c r="I88" s="3" t="inlineStr"/>
+      <c r="J88" s="3" t="inlineStr"/>
+      <c r="K88" s="3" t="inlineStr"/>
+      <c r="L88" s="3" t="inlineStr"/>
+      <c r="M88" s="3" t="inlineStr"/>
+      <c r="N88" s="3" t="inlineStr"/>
+      <c r="O88" s="3" t="inlineStr"/>
+      <c r="P88" s="3" t="inlineStr"/>
+      <c r="Q88" s="3" t="inlineStr"/>
+      <c r="R88" s="3" t="inlineStr"/>
+      <c r="S88" s="3" t="inlineStr"/>
+      <c r="T88" s="3" t="inlineStr"/>
+      <c r="U88" s="3" t="inlineStr"/>
+      <c r="V88" s="3" t="inlineStr"/>
+      <c r="W88" s="3" t="inlineStr"/>
+      <c r="X88" s="3" t="inlineStr"/>
+      <c r="Y88" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z88" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA88" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB88" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AC88" s="3" t="inlineStr"/>
+      <c r="AD88" s="3" t="inlineStr"/>
+      <c r="AE88" s="3" t="inlineStr"/>
+      <c r="AF88" s="3" t="inlineStr"/>
+    </row>
+    <row r="89" ht="22" customHeight="1">
+      <c r="A89" s="27" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr"/>
+      <c r="C89" s="3" t="inlineStr"/>
+      <c r="D89" s="3" t="inlineStr"/>
+      <c r="E89" s="3" t="inlineStr"/>
+      <c r="F89" s="3" t="inlineStr"/>
+      <c r="G89" s="3" t="inlineStr"/>
+      <c r="H89" s="3" t="inlineStr"/>
+      <c r="I89" s="3" t="inlineStr"/>
+      <c r="J89" s="3" t="inlineStr"/>
+      <c r="K89" s="3" t="inlineStr"/>
+      <c r="L89" s="3" t="inlineStr"/>
+      <c r="M89" s="3" t="inlineStr"/>
+      <c r="N89" s="3" t="inlineStr"/>
+      <c r="O89" s="3" t="inlineStr"/>
+      <c r="P89" s="3" t="inlineStr"/>
+      <c r="Q89" s="3" t="inlineStr"/>
+      <c r="R89" s="3" t="inlineStr"/>
+      <c r="S89" s="3" t="inlineStr"/>
+      <c r="T89" s="3" t="inlineStr"/>
+      <c r="U89" s="3" t="inlineStr"/>
+      <c r="V89" s="3" t="inlineStr"/>
+      <c r="W89" s="3" t="inlineStr"/>
+      <c r="X89" s="3" t="inlineStr"/>
+      <c r="Y89" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z89" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA89" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB89" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AC89" s="3" t="inlineStr"/>
+      <c r="AD89" s="3" t="inlineStr"/>
+      <c r="AE89" s="3" t="inlineStr"/>
+      <c r="AF89" s="3" t="inlineStr"/>
+    </row>
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" s="27" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr"/>
+      <c r="C90" s="3" t="inlineStr"/>
+      <c r="D90" s="3" t="inlineStr"/>
+      <c r="E90" s="3" t="inlineStr"/>
+      <c r="F90" s="3" t="inlineStr"/>
+      <c r="G90" s="3" t="inlineStr"/>
+      <c r="H90" s="3" t="inlineStr"/>
+      <c r="I90" s="3" t="inlineStr"/>
+      <c r="J90" s="3" t="inlineStr"/>
+      <c r="K90" s="3" t="inlineStr"/>
+      <c r="L90" s="3" t="inlineStr"/>
+      <c r="M90" s="3" t="inlineStr"/>
+      <c r="N90" s="3" t="inlineStr"/>
+      <c r="O90" s="3" t="inlineStr"/>
+      <c r="P90" s="3" t="inlineStr"/>
+      <c r="Q90" s="3" t="inlineStr"/>
+      <c r="R90" s="3" t="inlineStr"/>
+      <c r="S90" s="3" t="inlineStr"/>
+      <c r="T90" s="3" t="inlineStr"/>
+      <c r="U90" s="3" t="inlineStr"/>
+      <c r="V90" s="3" t="inlineStr"/>
+      <c r="W90" s="3" t="inlineStr"/>
+      <c r="X90" s="3" t="inlineStr"/>
+      <c r="Y90" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z90" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA90" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB90" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AC90" s="3" t="inlineStr"/>
+      <c r="AD90" s="3" t="inlineStr"/>
+      <c r="AE90" s="3" t="inlineStr"/>
+      <c r="AF90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91" ht="22" customHeight="1">
+      <c r="A91" s="27" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr"/>
+      <c r="C91" s="3" t="inlineStr"/>
+      <c r="D91" s="3" t="inlineStr"/>
+      <c r="E91" s="3" t="inlineStr"/>
+      <c r="F91" s="3" t="inlineStr"/>
+      <c r="G91" s="3" t="inlineStr"/>
+      <c r="H91" s="3" t="inlineStr"/>
+      <c r="I91" s="3" t="inlineStr"/>
+      <c r="J91" s="3" t="inlineStr"/>
+      <c r="K91" s="3" t="inlineStr"/>
+      <c r="L91" s="3" t="inlineStr"/>
+      <c r="M91" s="3" t="inlineStr"/>
+      <c r="N91" s="3" t="inlineStr"/>
+      <c r="O91" s="3" t="inlineStr"/>
+      <c r="P91" s="3" t="inlineStr"/>
+      <c r="Q91" s="3" t="inlineStr"/>
+      <c r="R91" s="3" t="inlineStr"/>
+      <c r="S91" s="3" t="inlineStr"/>
+      <c r="T91" s="3" t="inlineStr"/>
+      <c r="U91" s="3" t="inlineStr"/>
+      <c r="V91" s="3" t="inlineStr"/>
+      <c r="W91" s="3" t="inlineStr"/>
+      <c r="X91" s="3" t="inlineStr"/>
+      <c r="Y91" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z91" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA91" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB91" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AC91" s="3" t="inlineStr"/>
+      <c r="AD91" s="3" t="inlineStr"/>
+      <c r="AE91" s="3" t="inlineStr"/>
+      <c r="AF91" s="3" t="inlineStr"/>
+    </row>
+    <row r="92" ht="22" customHeight="1">
+      <c r="A92" s="27" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr"/>
+      <c r="C92" s="3" t="inlineStr"/>
+      <c r="D92" s="3" t="inlineStr"/>
+      <c r="E92" s="3" t="inlineStr"/>
+      <c r="F92" s="3" t="inlineStr"/>
+      <c r="G92" s="3" t="inlineStr"/>
+      <c r="H92" s="3" t="inlineStr"/>
+      <c r="I92" s="3" t="inlineStr"/>
+      <c r="J92" s="3" t="inlineStr"/>
+      <c r="K92" s="3" t="inlineStr"/>
+      <c r="L92" s="3" t="inlineStr"/>
+      <c r="M92" s="3" t="inlineStr"/>
+      <c r="N92" s="3" t="inlineStr"/>
+      <c r="O92" s="3" t="inlineStr"/>
+      <c r="P92" s="3" t="inlineStr"/>
+      <c r="Q92" s="3" t="inlineStr"/>
+      <c r="R92" s="3" t="inlineStr"/>
+      <c r="S92" s="3" t="inlineStr"/>
+      <c r="T92" s="3" t="inlineStr"/>
+      <c r="U92" s="3" t="inlineStr"/>
+      <c r="V92" s="3" t="inlineStr"/>
+      <c r="W92" s="3" t="inlineStr"/>
+      <c r="X92" s="3" t="inlineStr"/>
+      <c r="Y92" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z92" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA92" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB92" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AC92" s="3" t="inlineStr"/>
+      <c r="AD92" s="3" t="inlineStr"/>
+      <c r="AE92" s="3" t="inlineStr"/>
+      <c r="AF92" s="3" t="inlineStr"/>
+    </row>
+    <row r="93" ht="22" customHeight="1">
+      <c r="A93" s="27" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr"/>
+      <c r="C93" s="3" t="inlineStr"/>
+      <c r="D93" s="3" t="inlineStr"/>
+      <c r="E93" s="3" t="inlineStr"/>
+      <c r="F93" s="3" t="inlineStr"/>
+      <c r="G93" s="3" t="inlineStr"/>
+      <c r="H93" s="3" t="inlineStr"/>
+      <c r="I93" s="3" t="inlineStr"/>
+      <c r="J93" s="3" t="inlineStr"/>
+      <c r="K93" s="3" t="inlineStr"/>
+      <c r="L93" s="3" t="inlineStr"/>
+      <c r="M93" s="3" t="inlineStr"/>
+      <c r="N93" s="3" t="inlineStr"/>
+      <c r="O93" s="3" t="inlineStr"/>
+      <c r="P93" s="3" t="inlineStr"/>
+      <c r="Q93" s="3" t="inlineStr"/>
+      <c r="R93" s="3" t="inlineStr"/>
+      <c r="S93" s="3" t="inlineStr"/>
+      <c r="T93" s="3" t="inlineStr"/>
+      <c r="U93" s="3" t="inlineStr"/>
+      <c r="V93" s="3" t="inlineStr"/>
+      <c r="W93" s="3" t="inlineStr"/>
+      <c r="X93" s="3" t="inlineStr"/>
+      <c r="Y93" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z93" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA93" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB93" s="28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AC93" s="3" t="inlineStr"/>
+      <c r="AD93" s="3" t="inlineStr"/>
+      <c r="AE93" s="3" t="inlineStr"/>
+      <c r="AF93" s="3" t="inlineStr"/>
+    </row>
+    <row r="94" ht="22" customHeight="1">
+      <c r="A94" s="6" t="inlineStr"/>
+      <c r="B94" s="3" t="inlineStr"/>
+      <c r="C94" s="3" t="inlineStr"/>
+      <c r="D94" s="3" t="inlineStr"/>
+      <c r="E94" s="3" t="inlineStr"/>
+      <c r="F94" s="3" t="inlineStr"/>
+      <c r="G94" s="3" t="inlineStr"/>
+      <c r="H94" s="3" t="inlineStr"/>
+      <c r="I94" s="3" t="inlineStr"/>
+      <c r="J94" s="3" t="inlineStr"/>
+      <c r="K94" s="3" t="inlineStr"/>
+      <c r="L94" s="3" t="inlineStr"/>
+      <c r="M94" s="3" t="inlineStr"/>
+      <c r="N94" s="3" t="inlineStr"/>
+      <c r="O94" s="3" t="inlineStr"/>
+      <c r="P94" s="3" t="inlineStr"/>
+      <c r="Q94" s="3" t="inlineStr"/>
+      <c r="R94" s="3" t="inlineStr"/>
+      <c r="S94" s="3" t="inlineStr"/>
+      <c r="T94" s="3" t="inlineStr"/>
+      <c r="U94" s="3" t="inlineStr"/>
+      <c r="V94" s="3" t="inlineStr"/>
+      <c r="W94" s="3" t="inlineStr"/>
+      <c r="X94" s="3" t="inlineStr"/>
+      <c r="Y94" s="3" t="inlineStr"/>
+      <c r="Z94" s="3" t="inlineStr"/>
+      <c r="AA94" s="3" t="inlineStr"/>
+      <c r="AB94" s="3" t="inlineStr"/>
+      <c r="AC94" s="3" t="inlineStr"/>
+      <c r="AD94" s="3" t="inlineStr"/>
+      <c r="AE94" s="3" t="inlineStr"/>
+      <c r="AF94" s="3" t="inlineStr"/>
+    </row>
+    <row r="95" ht="22" customHeight="1">
+      <c r="A95" s="19" t="inlineStr">
         <is>
           <t>线体合计</t>
         </is>
       </c>
-      <c r="B74" s="24" t="n">
+      <c r="B95" s="29" t="n">
         <v>18</v>
       </c>
-      <c r="C74" s="24" t="n">
+      <c r="C95" s="29" t="n">
         <v>18</v>
       </c>
-      <c r="D74" s="24" t="n">
+      <c r="D95" s="29" t="n">
         <v>18</v>
       </c>
-      <c r="E74" s="24" t="inlineStr"/>
-      <c r="F74" s="24" t="inlineStr"/>
-      <c r="G74" s="24" t="n">
+      <c r="E95" s="29" t="n">
         <v>18</v>
       </c>
-      <c r="H74" s="24" t="n">
+      <c r="F95" s="29" t="n">
         <v>18</v>
       </c>
-      <c r="I74" s="24" t="n">
+      <c r="G95" s="29" t="n">
         <v>18</v>
       </c>
-      <c r="J74" s="24" t="n">
+      <c r="H95" s="29" t="n">
         <v>18</v>
       </c>
-      <c r="K74" s="24" t="n">
+      <c r="I95" s="29" t="n">
         <v>18</v>
       </c>
-      <c r="L74" s="24" t="inlineStr"/>
-      <c r="M74" s="24" t="inlineStr"/>
-      <c r="N74" s="24" t="inlineStr"/>
-      <c r="O74" s="24" t="inlineStr"/>
-      <c r="P74" s="24" t="inlineStr"/>
-      <c r="Q74" s="24" t="inlineStr"/>
-      <c r="R74" s="24" t="inlineStr"/>
-      <c r="S74" s="24" t="inlineStr"/>
-      <c r="T74" s="24" t="inlineStr"/>
-      <c r="U74" s="24" t="inlineStr"/>
-      <c r="V74" s="24" t="inlineStr"/>
-      <c r="W74" s="24" t="inlineStr"/>
-      <c r="X74" s="24" t="inlineStr"/>
-      <c r="Y74" s="24" t="inlineStr"/>
-      <c r="Z74" s="24" t="inlineStr"/>
-      <c r="AA74" s="24" t="inlineStr"/>
-      <c r="AB74" s="24" t="inlineStr"/>
-      <c r="AC74" s="24" t="inlineStr"/>
-      <c r="AD74" s="24" t="inlineStr"/>
-      <c r="AE74" s="24" t="inlineStr"/>
-      <c r="AF74" s="24" t="inlineStr"/>
-    </row>
-    <row r="75" ht="22" customHeight="1">
-      <c r="A75" s="23" t="inlineStr">
+      <c r="J95" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="K95" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="L95" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="M95" s="29" t="inlineStr"/>
+      <c r="N95" s="29" t="inlineStr"/>
+      <c r="O95" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="P95" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q95" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="R95" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="S95" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="T95" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="U95" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="V95" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="W95" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="X95" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y95" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z95" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA95" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB95" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC95" s="29" t="inlineStr"/>
+      <c r="AD95" s="29" t="inlineStr"/>
+      <c r="AE95" s="29" t="inlineStr"/>
+      <c r="AF95" s="29" t="inlineStr"/>
+    </row>
+    <row r="96" ht="22" customHeight="1">
+      <c r="A96" s="19" t="inlineStr">
         <is>
           <t>产能合计</t>
         </is>
       </c>
-      <c r="B75" s="24" t="n">
+      <c r="B96" s="29" t="n">
         <v>4140000</v>
       </c>
-      <c r="C75" s="24" t="n">
+      <c r="C96" s="29" t="n">
         <v>4140000</v>
       </c>
-      <c r="D75" s="24" t="n">
-        <v>3241476</v>
-      </c>
-      <c r="E75" s="24" t="inlineStr"/>
-      <c r="F75" s="24" t="inlineStr"/>
-      <c r="G75" s="24" t="n">
+      <c r="D96" s="29" t="n">
+        <v>4140000</v>
+      </c>
+      <c r="E96" s="29" t="n">
+        <v>4140000</v>
+      </c>
+      <c r="F96" s="29" t="n">
+        <v>4140000</v>
+      </c>
+      <c r="G96" s="29" t="n">
+        <v>4140000</v>
+      </c>
+      <c r="H96" s="29" t="n">
+        <v>4140000</v>
+      </c>
+      <c r="I96" s="29" t="n">
+        <v>4140000</v>
+      </c>
+      <c r="J96" s="29" t="n">
+        <v>4140000</v>
+      </c>
+      <c r="K96" s="29" t="n">
+        <v>4140000</v>
+      </c>
+      <c r="L96" s="29" t="n">
+        <v>2754162</v>
+      </c>
+      <c r="M96" s="29" t="inlineStr"/>
+      <c r="N96" s="29" t="inlineStr"/>
+      <c r="O96" s="29" t="n">
         <v>1656000</v>
       </c>
-      <c r="H75" s="24" t="n">
+      <c r="P96" s="29" t="n">
         <v>3312000</v>
       </c>
-      <c r="I75" s="24" t="n">
+      <c r="Q96" s="29" t="n">
         <v>3726000</v>
       </c>
-      <c r="J75" s="24" t="n">
+      <c r="R96" s="29" t="n">
         <v>3933000</v>
       </c>
-      <c r="K75" s="24" t="n">
+      <c r="S96" s="29" t="n">
         <v>4140000</v>
       </c>
-      <c r="L75" s="24" t="inlineStr"/>
-      <c r="M75" s="24" t="inlineStr"/>
-      <c r="N75" s="24" t="inlineStr"/>
-      <c r="O75" s="24" t="inlineStr"/>
-      <c r="P75" s="24" t="inlineStr"/>
-      <c r="Q75" s="24" t="inlineStr"/>
-      <c r="R75" s="24" t="inlineStr"/>
-      <c r="S75" s="24" t="inlineStr"/>
-      <c r="T75" s="24" t="inlineStr"/>
-      <c r="U75" s="24" t="inlineStr"/>
-      <c r="V75" s="24" t="inlineStr"/>
-      <c r="W75" s="24" t="inlineStr"/>
-      <c r="X75" s="24" t="inlineStr"/>
-      <c r="Y75" s="24" t="inlineStr"/>
-      <c r="Z75" s="24" t="inlineStr"/>
-      <c r="AA75" s="24" t="inlineStr"/>
-      <c r="AB75" s="24" t="inlineStr"/>
-      <c r="AC75" s="24" t="inlineStr"/>
-      <c r="AD75" s="24" t="inlineStr"/>
-      <c r="AE75" s="24" t="inlineStr"/>
-      <c r="AF75" s="24" t="inlineStr"/>
+      <c r="T96" s="29" t="n">
+        <v>4140000</v>
+      </c>
+      <c r="U96" s="29" t="n">
+        <v>4140000</v>
+      </c>
+      <c r="V96" s="29" t="n">
+        <v>4140000</v>
+      </c>
+      <c r="W96" s="29" t="n">
+        <v>4140000</v>
+      </c>
+      <c r="X96" s="29" t="n">
+        <v>4140000</v>
+      </c>
+      <c r="Y96" s="29" t="n">
+        <v>4140000</v>
+      </c>
+      <c r="Z96" s="29" t="n">
+        <v>4140000</v>
+      </c>
+      <c r="AA96" s="29" t="n">
+        <v>4140000</v>
+      </c>
+      <c r="AB96" s="29" t="n">
+        <v>4140000</v>
+      </c>
+      <c r="AC96" s="29" t="inlineStr"/>
+      <c r="AD96" s="29" t="inlineStr"/>
+      <c r="AE96" s="29" t="inlineStr"/>
+      <c r="AF96" s="29" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:AF20"/>
